--- a/API 명세서.xlsx
+++ b/API 명세서.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="93">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -550,10 +550,6 @@
   </si>
   <si>
     <t>유저 이메일 (이메일 형태의 데이터)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>userPassword</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1324,6 +1320,198 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1344,198 +1532,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1822,569 +1818,569 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:12" ht="54" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="69"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="2:12" ht="31.5" x14ac:dyDescent="0.3">
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="72"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="2:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="75"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="68"/>
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="76"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="78"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="71"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="76"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="78"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="76"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="78"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="71"/>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="76"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="78"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="71"/>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="76"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="78"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="71"/>
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="76"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="78"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="71"/>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="76"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="78"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="71"/>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="76"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="78"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="71"/>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="76"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="78"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="71"/>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="76"/>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="78"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="71"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="76"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
-      <c r="K15" s="78"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="71"/>
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="76"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="78"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="71"/>
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="76"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="78"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="71"/>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="76"/>
-      <c r="C18" s="77"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="77"/>
-      <c r="K18" s="78"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="71"/>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="76"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="78"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="71"/>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="76"/>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="77"/>
-      <c r="K20" s="78"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="71"/>
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="76"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="78"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="71"/>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="76"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="78"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="71"/>
       <c r="L22" s="3"/>
     </row>
     <row r="23" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="76"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="78"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="71"/>
       <c r="L23" s="3"/>
     </row>
     <row r="24" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="76"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
-      <c r="K24" s="78"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="71"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="76"/>
-      <c r="C25" s="77"/>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="77"/>
-      <c r="K25" s="78"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="71"/>
       <c r="L25" s="3"/>
     </row>
     <row r="26" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="76"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="77"/>
-      <c r="K26" s="78"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="71"/>
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="76"/>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="78"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="71"/>
       <c r="L27" s="3"/>
     </row>
     <row r="28" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="79"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="80"/>
-      <c r="J28" s="80"/>
-      <c r="K28" s="81"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="74"/>
       <c r="L28" s="3"/>
     </row>
     <row r="29" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="82" t="s">
+      <c r="B29" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="83"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="85" t="s">
+      <c r="C29" s="76"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="86"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="78"/>
+      <c r="I29" s="78"/>
+      <c r="J29" s="78"/>
+      <c r="K29" s="79"/>
       <c r="L29" s="3"/>
     </row>
     <row r="30" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="2:12" ht="41.25" x14ac:dyDescent="0.3">
-      <c r="B31" s="48" t="s">
+      <c r="B31" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="50"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="43"/>
     </row>
     <row r="32" spans="2:12" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="53"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="46"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B33" s="35" t="s">
+      <c r="B33" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="55"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="48"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B34" s="35"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="54"/>
-      <c r="J34" s="54"/>
-      <c r="K34" s="55"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="48"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35" s="35"/>
-      <c r="C35" s="54"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="54"/>
-      <c r="K35" s="55"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="48"/>
     </row>
     <row r="36" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="56"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="58"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="51"/>
     </row>
     <row r="37" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="42" t="s">
+      <c r="B37" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C37" s="43"/>
-      <c r="D37" s="59" t="s">
+      <c r="C37" s="33"/>
+      <c r="D37" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="E37" s="59"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="61" t="s">
+      <c r="E37" s="52"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="H37" s="62"/>
-      <c r="I37" s="63" t="s">
+      <c r="H37" s="55"/>
+      <c r="I37" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="J37" s="63"/>
-      <c r="K37" s="64"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="57"/>
     </row>
     <row r="38" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="42" t="s">
+      <c r="B38" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="44"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="34"/>
     </row>
     <row r="39" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B39" s="45" t="s">
+      <c r="B39" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C39" s="65"/>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="65"/>
-      <c r="J39" s="65"/>
-      <c r="K39" s="66"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="59"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28" t="s">
+      <c r="C40" s="39"/>
+      <c r="D40" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28" t="s">
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="K40" s="29"/>
+      <c r="K40" s="40"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="27"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="29"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="40"/>
     </row>
     <row r="42" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B42" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="34"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="24"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B43" s="30" t="s">
+      <c r="B43" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31" t="s">
+      <c r="C43" s="21"/>
+      <c r="D43" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31" t="s">
+      <c r="E43" s="21"/>
+      <c r="F43" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31" t="s">
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K43" s="32"/>
+      <c r="K43" s="22"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="5" t="s">
@@ -2407,152 +2403,152 @@
       <c r="K44" s="9"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28" t="s">
+      <c r="C45" s="39"/>
+      <c r="D45" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28" t="s">
+      <c r="E45" s="39"/>
+      <c r="F45" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28" t="s">
+      <c r="G45" s="39"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="K45" s="29"/>
+      <c r="K45" s="40"/>
     </row>
     <row r="46" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B46" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="34"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="23"/>
+      <c r="K46" s="24"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B47" s="35" t="s">
+      <c r="B47" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
-      <c r="J47" s="36"/>
-      <c r="K47" s="37"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
+      <c r="K47" s="27"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B48" s="38"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="36"/>
-      <c r="K48" s="37"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="26"/>
+      <c r="K48" s="27"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B49" s="38"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="37"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="27"/>
     </row>
     <row r="50" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="39"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="41"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="31"/>
     </row>
     <row r="51" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="42" t="s">
+      <c r="B51" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="43"/>
-      <c r="J51" s="43"/>
-      <c r="K51" s="44"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="34"/>
     </row>
     <row r="52" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B52" s="45" t="s">
+      <c r="B52" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="47"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="36"/>
+      <c r="J52" s="36"/>
+      <c r="K52" s="37"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B53" s="30" t="s">
+      <c r="B53" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31" t="s">
+      <c r="C53" s="21"/>
+      <c r="D53" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31" t="s">
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K53" s="32"/>
+      <c r="K53" s="22"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28" t="s">
+      <c r="C54" s="39"/>
+      <c r="D54" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="28" t="s">
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="K54" s="29"/>
+      <c r="K54" s="40"/>
     </row>
     <row r="55" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B55" s="10" t="s">
@@ -2569,24 +2565,24 @@
       <c r="K55" s="12"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B56" s="30" t="s">
+      <c r="B56" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="31"/>
-      <c r="D56" s="31" t="s">
+      <c r="C56" s="21"/>
+      <c r="D56" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E56" s="31"/>
-      <c r="F56" s="31" t="s">
+      <c r="E56" s="21"/>
+      <c r="F56" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G56" s="31"/>
-      <c r="H56" s="31"/>
-      <c r="I56" s="31"/>
-      <c r="J56" s="31" t="s">
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K56" s="32"/>
+      <c r="K56" s="22"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" s="5" t="s">
@@ -2649,24 +2645,24 @@
       <c r="K59" s="9"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28" t="s">
+      <c r="C60" s="39"/>
+      <c r="D60" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28" t="s">
+      <c r="E60" s="39"/>
+      <c r="F60" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-      <c r="J60" s="28" t="s">
+      <c r="G60" s="39"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="K60" s="29"/>
+      <c r="K60" s="40"/>
     </row>
     <row r="61" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B61" s="10" t="s">
@@ -2698,310 +2694,310 @@
     </row>
     <row r="63" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="64" spans="2:11" ht="41.25" x14ac:dyDescent="0.3">
-      <c r="B64" s="48" t="s">
+      <c r="B64" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C64" s="49"/>
-      <c r="D64" s="49"/>
-      <c r="E64" s="49"/>
-      <c r="F64" s="49"/>
-      <c r="G64" s="49"/>
-      <c r="H64" s="49"/>
-      <c r="I64" s="49"/>
-      <c r="J64" s="49"/>
-      <c r="K64" s="50"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="42"/>
+      <c r="K64" s="43"/>
     </row>
     <row r="65" spans="2:11" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="B65" s="51" t="s">
+      <c r="B65" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="52"/>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
-      <c r="H65" s="52"/>
-      <c r="I65" s="52"/>
-      <c r="J65" s="52"/>
-      <c r="K65" s="53"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="45"/>
+      <c r="I65" s="45"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="46"/>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B66" s="35" t="s">
+      <c r="B66" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C66" s="54"/>
-      <c r="D66" s="54"/>
-      <c r="E66" s="54"/>
-      <c r="F66" s="54"/>
-      <c r="G66" s="54"/>
-      <c r="H66" s="54"/>
-      <c r="I66" s="54"/>
-      <c r="J66" s="54"/>
-      <c r="K66" s="55"/>
+      <c r="C66" s="47"/>
+      <c r="D66" s="47"/>
+      <c r="E66" s="47"/>
+      <c r="F66" s="47"/>
+      <c r="G66" s="47"/>
+      <c r="H66" s="47"/>
+      <c r="I66" s="47"/>
+      <c r="J66" s="47"/>
+      <c r="K66" s="48"/>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B67" s="35"/>
-      <c r="C67" s="54"/>
-      <c r="D67" s="54"/>
-      <c r="E67" s="54"/>
-      <c r="F67" s="54"/>
-      <c r="G67" s="54"/>
-      <c r="H67" s="54"/>
-      <c r="I67" s="54"/>
-      <c r="J67" s="54"/>
-      <c r="K67" s="55"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="47"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="47"/>
+      <c r="J67" s="47"/>
+      <c r="K67" s="48"/>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B68" s="35"/>
-      <c r="C68" s="54"/>
-      <c r="D68" s="54"/>
-      <c r="E68" s="54"/>
-      <c r="F68" s="54"/>
-      <c r="G68" s="54"/>
-      <c r="H68" s="54"/>
-      <c r="I68" s="54"/>
-      <c r="J68" s="54"/>
-      <c r="K68" s="55"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="47"/>
+      <c r="D68" s="47"/>
+      <c r="E68" s="47"/>
+      <c r="F68" s="47"/>
+      <c r="G68" s="47"/>
+      <c r="H68" s="47"/>
+      <c r="I68" s="47"/>
+      <c r="J68" s="47"/>
+      <c r="K68" s="48"/>
     </row>
     <row r="69" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="56"/>
-      <c r="C69" s="57"/>
-      <c r="D69" s="57"/>
-      <c r="E69" s="57"/>
-      <c r="F69" s="57"/>
-      <c r="G69" s="57"/>
-      <c r="H69" s="57"/>
-      <c r="I69" s="57"/>
-      <c r="J69" s="57"/>
-      <c r="K69" s="58"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="50"/>
+      <c r="E69" s="50"/>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
+      <c r="H69" s="50"/>
+      <c r="I69" s="50"/>
+      <c r="J69" s="50"/>
+      <c r="K69" s="51"/>
     </row>
     <row r="70" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="42" t="s">
+      <c r="B70" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="43"/>
-      <c r="D70" s="59" t="s">
+      <c r="C70" s="33"/>
+      <c r="D70" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="E70" s="59"/>
-      <c r="F70" s="60"/>
-      <c r="G70" s="61" t="s">
+      <c r="E70" s="52"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="H70" s="62"/>
-      <c r="I70" s="63" t="s">
+      <c r="H70" s="55"/>
+      <c r="I70" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="J70" s="63"/>
-      <c r="K70" s="64"/>
+      <c r="J70" s="56"/>
+      <c r="K70" s="57"/>
     </row>
     <row r="71" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="42" t="s">
+      <c r="B71" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C71" s="43"/>
-      <c r="D71" s="43"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="43"/>
-      <c r="H71" s="43"/>
-      <c r="I71" s="43"/>
-      <c r="J71" s="43"/>
-      <c r="K71" s="44"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="33"/>
+      <c r="K71" s="34"/>
     </row>
     <row r="72" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B72" s="45" t="s">
+      <c r="B72" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C72" s="65"/>
-      <c r="D72" s="65"/>
-      <c r="E72" s="65"/>
-      <c r="F72" s="65"/>
-      <c r="G72" s="65"/>
-      <c r="H72" s="65"/>
-      <c r="I72" s="65"/>
-      <c r="J72" s="65"/>
-      <c r="K72" s="66"/>
+      <c r="C72" s="58"/>
+      <c r="D72" s="58"/>
+      <c r="E72" s="58"/>
+      <c r="F72" s="58"/>
+      <c r="G72" s="58"/>
+      <c r="H72" s="58"/>
+      <c r="I72" s="58"/>
+      <c r="J72" s="58"/>
+      <c r="K72" s="59"/>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B73" s="30" t="s">
+      <c r="B73" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C73" s="31"/>
-      <c r="D73" s="31" t="s">
+      <c r="C73" s="21"/>
+      <c r="D73" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="E73" s="31"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="31"/>
-      <c r="I73" s="31"/>
-      <c r="J73" s="31" t="s">
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K73" s="32"/>
+      <c r="K73" s="22"/>
     </row>
     <row r="74" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B74" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C74" s="33"/>
-      <c r="D74" s="33"/>
-      <c r="E74" s="33"/>
-      <c r="F74" s="33"/>
-      <c r="G74" s="33"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="33"/>
-      <c r="J74" s="33"/>
-      <c r="K74" s="34"/>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="23"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="23"/>
+      <c r="K74" s="24"/>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B75" s="30" t="s">
+      <c r="B75" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31" t="s">
+      <c r="C75" s="21"/>
+      <c r="D75" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31" t="s">
+      <c r="E75" s="21"/>
+      <c r="F75" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
-      <c r="J75" s="31" t="s">
+      <c r="G75" s="21"/>
+      <c r="H75" s="21"/>
+      <c r="I75" s="21"/>
+      <c r="J75" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K75" s="32"/>
+      <c r="K75" s="22"/>
     </row>
     <row r="76" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B76" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C76" s="33"/>
-      <c r="D76" s="33"/>
-      <c r="E76" s="33"/>
-      <c r="F76" s="33"/>
-      <c r="G76" s="33"/>
-      <c r="H76" s="33"/>
-      <c r="I76" s="33"/>
-      <c r="J76" s="33"/>
-      <c r="K76" s="34"/>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="23"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="23"/>
+      <c r="I76" s="23"/>
+      <c r="J76" s="23"/>
+      <c r="K76" s="24"/>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B77" s="35" t="s">
+      <c r="B77" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C77" s="36"/>
-      <c r="D77" s="36"/>
-      <c r="E77" s="36"/>
-      <c r="F77" s="36"/>
-      <c r="G77" s="36"/>
-      <c r="H77" s="36"/>
-      <c r="I77" s="36"/>
-      <c r="J77" s="36"/>
-      <c r="K77" s="37"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+      <c r="K77" s="27"/>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B78" s="38"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36"/>
-      <c r="J78" s="36"/>
-      <c r="K78" s="37"/>
+      <c r="B78" s="28"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="27"/>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B79" s="38"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
-      <c r="J79" s="36"/>
-      <c r="K79" s="37"/>
+      <c r="B79" s="28"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="26"/>
+      <c r="J79" s="26"/>
+      <c r="K79" s="27"/>
     </row>
     <row r="80" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="39"/>
-      <c r="C80" s="40"/>
-      <c r="D80" s="40"/>
-      <c r="E80" s="40"/>
-      <c r="F80" s="40"/>
-      <c r="G80" s="40"/>
-      <c r="H80" s="40"/>
-      <c r="I80" s="40"/>
-      <c r="J80" s="40"/>
-      <c r="K80" s="41"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
+      <c r="H80" s="30"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="30"/>
+      <c r="K80" s="31"/>
     </row>
     <row r="81" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="42" t="s">
+      <c r="B81" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C81" s="43"/>
-      <c r="D81" s="43"/>
-      <c r="E81" s="43"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="43"/>
-      <c r="H81" s="43"/>
-      <c r="I81" s="43"/>
-      <c r="J81" s="43"/>
-      <c r="K81" s="44"/>
+      <c r="C81" s="33"/>
+      <c r="D81" s="33"/>
+      <c r="E81" s="33"/>
+      <c r="F81" s="33"/>
+      <c r="G81" s="33"/>
+      <c r="H81" s="33"/>
+      <c r="I81" s="33"/>
+      <c r="J81" s="33"/>
+      <c r="K81" s="34"/>
     </row>
     <row r="82" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B82" s="45" t="s">
+      <c r="B82" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C82" s="46"/>
-      <c r="D82" s="46"/>
-      <c r="E82" s="46"/>
-      <c r="F82" s="46"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="46"/>
-      <c r="I82" s="46"/>
-      <c r="J82" s="46"/>
-      <c r="K82" s="47"/>
+      <c r="C82" s="36"/>
+      <c r="D82" s="36"/>
+      <c r="E82" s="36"/>
+      <c r="F82" s="36"/>
+      <c r="G82" s="36"/>
+      <c r="H82" s="36"/>
+      <c r="I82" s="36"/>
+      <c r="J82" s="36"/>
+      <c r="K82" s="37"/>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B83" s="30" t="s">
+      <c r="B83" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C83" s="31"/>
-      <c r="D83" s="31" t="s">
+      <c r="C83" s="21"/>
+      <c r="D83" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="E83" s="31"/>
-      <c r="F83" s="31"/>
-      <c r="G83" s="31"/>
-      <c r="H83" s="31"/>
-      <c r="I83" s="31"/>
-      <c r="J83" s="31" t="s">
+      <c r="E83" s="21"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="21"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K83" s="32"/>
+      <c r="K83" s="22"/>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B84" s="27" t="s">
+      <c r="B84" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28" t="s">
+      <c r="C84" s="39"/>
+      <c r="D84" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="28"/>
-      <c r="J84" s="28" t="s">
+      <c r="E84" s="39"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="39"/>
+      <c r="I84" s="39"/>
+      <c r="J84" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="K84" s="29"/>
+      <c r="K84" s="40"/>
     </row>
     <row r="85" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B85" s="10" t="s">
@@ -3018,24 +3014,24 @@
       <c r="K85" s="12"/>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B86" s="30" t="s">
+      <c r="B86" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="31"/>
-      <c r="D86" s="31" t="s">
+      <c r="C86" s="21"/>
+      <c r="D86" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="31"/>
-      <c r="F86" s="31" t="s">
+      <c r="E86" s="21"/>
+      <c r="F86" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G86" s="31"/>
-      <c r="H86" s="31"/>
-      <c r="I86" s="31"/>
-      <c r="J86" s="31" t="s">
+      <c r="G86" s="21"/>
+      <c r="H86" s="21"/>
+      <c r="I86" s="21"/>
+      <c r="J86" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K86" s="32"/>
+      <c r="K86" s="22"/>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B87" s="5" t="s">
@@ -3098,24 +3094,24 @@
       <c r="K89" s="9"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B90" s="27" t="s">
+      <c r="B90" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C90" s="28"/>
-      <c r="D90" s="28" t="s">
+      <c r="C90" s="39"/>
+      <c r="D90" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="E90" s="28"/>
-      <c r="F90" s="28" t="s">
+      <c r="E90" s="39"/>
+      <c r="F90" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="G90" s="28"/>
-      <c r="H90" s="28"/>
-      <c r="I90" s="28"/>
-      <c r="J90" s="28" t="s">
+      <c r="G90" s="39"/>
+      <c r="H90" s="39"/>
+      <c r="I90" s="39"/>
+      <c r="J90" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="K90" s="29"/>
+      <c r="K90" s="40"/>
     </row>
     <row r="91" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B91" s="10" t="s">
@@ -3147,330 +3143,330 @@
     </row>
     <row r="93" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="94" spans="2:11" ht="41.25" x14ac:dyDescent="0.3">
-      <c r="B94" s="48" t="s">
+      <c r="B94" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C94" s="49"/>
-      <c r="D94" s="49"/>
-      <c r="E94" s="49"/>
-      <c r="F94" s="49"/>
-      <c r="G94" s="49"/>
-      <c r="H94" s="49"/>
-      <c r="I94" s="49"/>
-      <c r="J94" s="49"/>
-      <c r="K94" s="50"/>
+      <c r="C94" s="42"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="42"/>
+      <c r="F94" s="42"/>
+      <c r="G94" s="42"/>
+      <c r="H94" s="42"/>
+      <c r="I94" s="42"/>
+      <c r="J94" s="42"/>
+      <c r="K94" s="43"/>
     </row>
     <row r="95" spans="2:11" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="B95" s="51" t="s">
+      <c r="B95" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C95" s="52"/>
-      <c r="D95" s="52"/>
-      <c r="E95" s="52"/>
-      <c r="F95" s="52"/>
-      <c r="G95" s="52"/>
-      <c r="H95" s="52"/>
-      <c r="I95" s="52"/>
-      <c r="J95" s="52"/>
-      <c r="K95" s="53"/>
+      <c r="C95" s="45"/>
+      <c r="D95" s="45"/>
+      <c r="E95" s="45"/>
+      <c r="F95" s="45"/>
+      <c r="G95" s="45"/>
+      <c r="H95" s="45"/>
+      <c r="I95" s="45"/>
+      <c r="J95" s="45"/>
+      <c r="K95" s="46"/>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B96" s="35" t="s">
+      <c r="B96" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C96" s="54"/>
-      <c r="D96" s="54"/>
-      <c r="E96" s="54"/>
-      <c r="F96" s="54"/>
-      <c r="G96" s="54"/>
-      <c r="H96" s="54"/>
-      <c r="I96" s="54"/>
-      <c r="J96" s="54"/>
-      <c r="K96" s="55"/>
+      <c r="C96" s="47"/>
+      <c r="D96" s="47"/>
+      <c r="E96" s="47"/>
+      <c r="F96" s="47"/>
+      <c r="G96" s="47"/>
+      <c r="H96" s="47"/>
+      <c r="I96" s="47"/>
+      <c r="J96" s="47"/>
+      <c r="K96" s="48"/>
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B97" s="35"/>
-      <c r="C97" s="54"/>
-      <c r="D97" s="54"/>
-      <c r="E97" s="54"/>
-      <c r="F97" s="54"/>
-      <c r="G97" s="54"/>
-      <c r="H97" s="54"/>
-      <c r="I97" s="54"/>
-      <c r="J97" s="54"/>
-      <c r="K97" s="55"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="47"/>
+      <c r="D97" s="47"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="47"/>
+      <c r="G97" s="47"/>
+      <c r="H97" s="47"/>
+      <c r="I97" s="47"/>
+      <c r="J97" s="47"/>
+      <c r="K97" s="48"/>
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B98" s="35"/>
-      <c r="C98" s="54"/>
-      <c r="D98" s="54"/>
-      <c r="E98" s="54"/>
-      <c r="F98" s="54"/>
-      <c r="G98" s="54"/>
-      <c r="H98" s="54"/>
-      <c r="I98" s="54"/>
-      <c r="J98" s="54"/>
-      <c r="K98" s="55"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="47"/>
+      <c r="D98" s="47"/>
+      <c r="E98" s="47"/>
+      <c r="F98" s="47"/>
+      <c r="G98" s="47"/>
+      <c r="H98" s="47"/>
+      <c r="I98" s="47"/>
+      <c r="J98" s="47"/>
+      <c r="K98" s="48"/>
     </row>
     <row r="99" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="56"/>
-      <c r="C99" s="57"/>
-      <c r="D99" s="57"/>
-      <c r="E99" s="57"/>
-      <c r="F99" s="57"/>
-      <c r="G99" s="57"/>
-      <c r="H99" s="57"/>
-      <c r="I99" s="57"/>
-      <c r="J99" s="57"/>
-      <c r="K99" s="58"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="50"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="50"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
+      <c r="H99" s="50"/>
+      <c r="I99" s="50"/>
+      <c r="J99" s="50"/>
+      <c r="K99" s="51"/>
     </row>
     <row r="100" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B100" s="42" t="s">
+      <c r="B100" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C100" s="43"/>
-      <c r="D100" s="59" t="s">
+      <c r="C100" s="33"/>
+      <c r="D100" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="E100" s="59"/>
-      <c r="F100" s="60"/>
-      <c r="G100" s="61" t="s">
+      <c r="E100" s="52"/>
+      <c r="F100" s="53"/>
+      <c r="G100" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="H100" s="62"/>
-      <c r="I100" s="63" t="s">
+      <c r="H100" s="55"/>
+      <c r="I100" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="J100" s="63"/>
-      <c r="K100" s="64"/>
+      <c r="J100" s="56"/>
+      <c r="K100" s="57"/>
     </row>
     <row r="101" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="42" t="s">
+      <c r="B101" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C101" s="43"/>
-      <c r="D101" s="43"/>
-      <c r="E101" s="43"/>
-      <c r="F101" s="43"/>
-      <c r="G101" s="43"/>
-      <c r="H101" s="43"/>
-      <c r="I101" s="43"/>
-      <c r="J101" s="43"/>
-      <c r="K101" s="44"/>
+      <c r="C101" s="33"/>
+      <c r="D101" s="33"/>
+      <c r="E101" s="33"/>
+      <c r="F101" s="33"/>
+      <c r="G101" s="33"/>
+      <c r="H101" s="33"/>
+      <c r="I101" s="33"/>
+      <c r="J101" s="33"/>
+      <c r="K101" s="34"/>
     </row>
     <row r="102" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B102" s="45" t="s">
+      <c r="B102" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C102" s="65"/>
-      <c r="D102" s="65"/>
-      <c r="E102" s="65"/>
-      <c r="F102" s="65"/>
-      <c r="G102" s="65"/>
-      <c r="H102" s="65"/>
-      <c r="I102" s="65"/>
-      <c r="J102" s="65"/>
-      <c r="K102" s="66"/>
+      <c r="C102" s="58"/>
+      <c r="D102" s="58"/>
+      <c r="E102" s="58"/>
+      <c r="F102" s="58"/>
+      <c r="G102" s="58"/>
+      <c r="H102" s="58"/>
+      <c r="I102" s="58"/>
+      <c r="J102" s="58"/>
+      <c r="K102" s="59"/>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B103" s="30" t="s">
+      <c r="B103" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C103" s="31"/>
-      <c r="D103" s="31" t="s">
+      <c r="C103" s="21"/>
+      <c r="D103" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E103" s="31"/>
-      <c r="F103" s="31"/>
-      <c r="G103" s="31"/>
-      <c r="H103" s="31"/>
-      <c r="I103" s="31"/>
-      <c r="J103" s="31" t="s">
+      <c r="E103" s="21"/>
+      <c r="F103" s="21"/>
+      <c r="G103" s="21"/>
+      <c r="H103" s="21"/>
+      <c r="I103" s="21"/>
+      <c r="J103" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K103" s="32"/>
+      <c r="K103" s="22"/>
     </row>
     <row r="104" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B104" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C104" s="33"/>
-      <c r="D104" s="33"/>
-      <c r="E104" s="33"/>
-      <c r="F104" s="33"/>
-      <c r="G104" s="33"/>
-      <c r="H104" s="33"/>
-      <c r="I104" s="33"/>
-      <c r="J104" s="33"/>
-      <c r="K104" s="34"/>
+      <c r="C104" s="23"/>
+      <c r="D104" s="23"/>
+      <c r="E104" s="23"/>
+      <c r="F104" s="23"/>
+      <c r="G104" s="23"/>
+      <c r="H104" s="23"/>
+      <c r="I104" s="23"/>
+      <c r="J104" s="23"/>
+      <c r="K104" s="24"/>
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B105" s="30" t="s">
+      <c r="B105" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C105" s="31"/>
-      <c r="D105" s="31" t="s">
+      <c r="C105" s="21"/>
+      <c r="D105" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="31"/>
-      <c r="F105" s="31" t="s">
+      <c r="E105" s="21"/>
+      <c r="F105" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G105" s="31"/>
-      <c r="H105" s="31"/>
-      <c r="I105" s="31"/>
-      <c r="J105" s="31" t="s">
+      <c r="G105" s="21"/>
+      <c r="H105" s="21"/>
+      <c r="I105" s="21"/>
+      <c r="J105" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K105" s="32"/>
+      <c r="K105" s="22"/>
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B106" s="26" t="s">
+      <c r="B106" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C106" s="23"/>
-      <c r="D106" s="23" t="s">
+      <c r="C106" s="17"/>
+      <c r="D106" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E106" s="23"/>
-      <c r="F106" s="23" t="s">
+      <c r="E106" s="17"/>
+      <c r="F106" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G106" s="23"/>
-      <c r="H106" s="23"/>
-      <c r="I106" s="23"/>
-      <c r="J106" s="23" t="s">
+      <c r="G106" s="17"/>
+      <c r="H106" s="17"/>
+      <c r="I106" s="17"/>
+      <c r="J106" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="K106" s="24"/>
+      <c r="K106" s="19"/>
     </row>
     <row r="107" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B107" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C107" s="33"/>
-      <c r="D107" s="33"/>
-      <c r="E107" s="33"/>
-      <c r="F107" s="33"/>
-      <c r="G107" s="33"/>
-      <c r="H107" s="33"/>
-      <c r="I107" s="33"/>
-      <c r="J107" s="33"/>
-      <c r="K107" s="34"/>
+      <c r="C107" s="23"/>
+      <c r="D107" s="23"/>
+      <c r="E107" s="23"/>
+      <c r="F107" s="23"/>
+      <c r="G107" s="23"/>
+      <c r="H107" s="23"/>
+      <c r="I107" s="23"/>
+      <c r="J107" s="23"/>
+      <c r="K107" s="24"/>
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B108" s="35" t="s">
+      <c r="B108" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C108" s="36"/>
-      <c r="D108" s="36"/>
-      <c r="E108" s="36"/>
-      <c r="F108" s="36"/>
-      <c r="G108" s="36"/>
-      <c r="H108" s="36"/>
-      <c r="I108" s="36"/>
-      <c r="J108" s="36"/>
-      <c r="K108" s="37"/>
+      <c r="C108" s="26"/>
+      <c r="D108" s="26"/>
+      <c r="E108" s="26"/>
+      <c r="F108" s="26"/>
+      <c r="G108" s="26"/>
+      <c r="H108" s="26"/>
+      <c r="I108" s="26"/>
+      <c r="J108" s="26"/>
+      <c r="K108" s="27"/>
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B109" s="38"/>
-      <c r="C109" s="36"/>
-      <c r="D109" s="36"/>
-      <c r="E109" s="36"/>
-      <c r="F109" s="36"/>
-      <c r="G109" s="36"/>
-      <c r="H109" s="36"/>
-      <c r="I109" s="36"/>
-      <c r="J109" s="36"/>
-      <c r="K109" s="37"/>
+      <c r="B109" s="28"/>
+      <c r="C109" s="26"/>
+      <c r="D109" s="26"/>
+      <c r="E109" s="26"/>
+      <c r="F109" s="26"/>
+      <c r="G109" s="26"/>
+      <c r="H109" s="26"/>
+      <c r="I109" s="26"/>
+      <c r="J109" s="26"/>
+      <c r="K109" s="27"/>
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B110" s="38"/>
-      <c r="C110" s="36"/>
-      <c r="D110" s="36"/>
-      <c r="E110" s="36"/>
-      <c r="F110" s="36"/>
-      <c r="G110" s="36"/>
-      <c r="H110" s="36"/>
-      <c r="I110" s="36"/>
-      <c r="J110" s="36"/>
-      <c r="K110" s="37"/>
+      <c r="B110" s="28"/>
+      <c r="C110" s="26"/>
+      <c r="D110" s="26"/>
+      <c r="E110" s="26"/>
+      <c r="F110" s="26"/>
+      <c r="G110" s="26"/>
+      <c r="H110" s="26"/>
+      <c r="I110" s="26"/>
+      <c r="J110" s="26"/>
+      <c r="K110" s="27"/>
     </row>
     <row r="111" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B111" s="39"/>
-      <c r="C111" s="40"/>
-      <c r="D111" s="40"/>
-      <c r="E111" s="40"/>
-      <c r="F111" s="40"/>
-      <c r="G111" s="40"/>
-      <c r="H111" s="40"/>
-      <c r="I111" s="40"/>
-      <c r="J111" s="40"/>
-      <c r="K111" s="41"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="30"/>
+      <c r="D111" s="30"/>
+      <c r="E111" s="30"/>
+      <c r="F111" s="30"/>
+      <c r="G111" s="30"/>
+      <c r="H111" s="30"/>
+      <c r="I111" s="30"/>
+      <c r="J111" s="30"/>
+      <c r="K111" s="31"/>
     </row>
     <row r="112" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B112" s="42" t="s">
+      <c r="B112" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C112" s="43"/>
-      <c r="D112" s="43"/>
-      <c r="E112" s="43"/>
-      <c r="F112" s="43"/>
-      <c r="G112" s="43"/>
-      <c r="H112" s="43"/>
-      <c r="I112" s="43"/>
-      <c r="J112" s="43"/>
-      <c r="K112" s="44"/>
+      <c r="C112" s="33"/>
+      <c r="D112" s="33"/>
+      <c r="E112" s="33"/>
+      <c r="F112" s="33"/>
+      <c r="G112" s="33"/>
+      <c r="H112" s="33"/>
+      <c r="I112" s="33"/>
+      <c r="J112" s="33"/>
+      <c r="K112" s="34"/>
     </row>
     <row r="113" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B113" s="45" t="s">
+      <c r="B113" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C113" s="46"/>
-      <c r="D113" s="46"/>
-      <c r="E113" s="46"/>
-      <c r="F113" s="46"/>
-      <c r="G113" s="46"/>
-      <c r="H113" s="46"/>
-      <c r="I113" s="46"/>
-      <c r="J113" s="46"/>
-      <c r="K113" s="47"/>
+      <c r="C113" s="36"/>
+      <c r="D113" s="36"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36"/>
+      <c r="G113" s="36"/>
+      <c r="H113" s="36"/>
+      <c r="I113" s="36"/>
+      <c r="J113" s="36"/>
+      <c r="K113" s="37"/>
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B114" s="30" t="s">
+      <c r="B114" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C114" s="31"/>
-      <c r="D114" s="31" t="s">
+      <c r="C114" s="21"/>
+      <c r="D114" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E114" s="31"/>
-      <c r="F114" s="31"/>
-      <c r="G114" s="31"/>
-      <c r="H114" s="31"/>
-      <c r="I114" s="31"/>
-      <c r="J114" s="31" t="s">
+      <c r="E114" s="21"/>
+      <c r="F114" s="21"/>
+      <c r="G114" s="21"/>
+      <c r="H114" s="21"/>
+      <c r="I114" s="21"/>
+      <c r="J114" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K114" s="32"/>
+      <c r="K114" s="22"/>
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B115" s="27" t="s">
+      <c r="B115" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C115" s="28"/>
-      <c r="D115" s="28" t="s">
+      <c r="C115" s="39"/>
+      <c r="D115" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E115" s="28"/>
-      <c r="F115" s="28"/>
-      <c r="G115" s="28"/>
-      <c r="H115" s="28"/>
-      <c r="I115" s="28"/>
-      <c r="J115" s="28" t="s">
+      <c r="E115" s="39"/>
+      <c r="F115" s="39"/>
+      <c r="G115" s="39"/>
+      <c r="H115" s="39"/>
+      <c r="I115" s="39"/>
+      <c r="J115" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="K115" s="29"/>
+      <c r="K115" s="40"/>
     </row>
     <row r="116" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B116" s="10" t="s">
@@ -3487,24 +3483,24 @@
       <c r="K116" s="12"/>
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B117" s="30" t="s">
+      <c r="B117" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C117" s="31"/>
-      <c r="D117" s="31" t="s">
+      <c r="C117" s="21"/>
+      <c r="D117" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="31"/>
-      <c r="F117" s="31" t="s">
+      <c r="E117" s="21"/>
+      <c r="F117" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G117" s="31"/>
-      <c r="H117" s="31"/>
-      <c r="I117" s="31"/>
-      <c r="J117" s="31" t="s">
+      <c r="G117" s="21"/>
+      <c r="H117" s="21"/>
+      <c r="I117" s="21"/>
+      <c r="J117" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K117" s="32"/>
+      <c r="K117" s="22"/>
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B118" s="5" t="s">
@@ -3576,331 +3572,331 @@
     </row>
     <row r="122" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="123" spans="2:11" ht="41.25" x14ac:dyDescent="0.3">
-      <c r="B123" s="48" t="s">
+      <c r="B123" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="C123" s="49"/>
-      <c r="D123" s="49"/>
-      <c r="E123" s="49"/>
-      <c r="F123" s="49"/>
-      <c r="G123" s="49"/>
-      <c r="H123" s="49"/>
-      <c r="I123" s="49"/>
-      <c r="J123" s="49"/>
-      <c r="K123" s="50"/>
+      <c r="C123" s="42"/>
+      <c r="D123" s="42"/>
+      <c r="E123" s="42"/>
+      <c r="F123" s="42"/>
+      <c r="G123" s="42"/>
+      <c r="H123" s="42"/>
+      <c r="I123" s="42"/>
+      <c r="J123" s="42"/>
+      <c r="K123" s="43"/>
     </row>
     <row r="124" spans="2:11" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="B124" s="51" t="s">
+      <c r="B124" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C124" s="52"/>
-      <c r="D124" s="52"/>
-      <c r="E124" s="52"/>
-      <c r="F124" s="52"/>
-      <c r="G124" s="52"/>
-      <c r="H124" s="52"/>
-      <c r="I124" s="52"/>
-      <c r="J124" s="52"/>
-      <c r="K124" s="53"/>
+      <c r="C124" s="45"/>
+      <c r="D124" s="45"/>
+      <c r="E124" s="45"/>
+      <c r="F124" s="45"/>
+      <c r="G124" s="45"/>
+      <c r="H124" s="45"/>
+      <c r="I124" s="45"/>
+      <c r="J124" s="45"/>
+      <c r="K124" s="46"/>
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B125" s="35" t="s">
+      <c r="B125" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C125" s="54"/>
-      <c r="D125" s="54"/>
-      <c r="E125" s="54"/>
-      <c r="F125" s="54"/>
-      <c r="G125" s="54"/>
-      <c r="H125" s="54"/>
-      <c r="I125" s="54"/>
-      <c r="J125" s="54"/>
-      <c r="K125" s="55"/>
+      <c r="C125" s="47"/>
+      <c r="D125" s="47"/>
+      <c r="E125" s="47"/>
+      <c r="F125" s="47"/>
+      <c r="G125" s="47"/>
+      <c r="H125" s="47"/>
+      <c r="I125" s="47"/>
+      <c r="J125" s="47"/>
+      <c r="K125" s="48"/>
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B126" s="35"/>
-      <c r="C126" s="54"/>
-      <c r="D126" s="54"/>
-      <c r="E126" s="54"/>
-      <c r="F126" s="54"/>
-      <c r="G126" s="54"/>
-      <c r="H126" s="54"/>
-      <c r="I126" s="54"/>
-      <c r="J126" s="54"/>
-      <c r="K126" s="55"/>
+      <c r="B126" s="25"/>
+      <c r="C126" s="47"/>
+      <c r="D126" s="47"/>
+      <c r="E126" s="47"/>
+      <c r="F126" s="47"/>
+      <c r="G126" s="47"/>
+      <c r="H126" s="47"/>
+      <c r="I126" s="47"/>
+      <c r="J126" s="47"/>
+      <c r="K126" s="48"/>
     </row>
     <row r="127" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B127" s="35"/>
-      <c r="C127" s="54"/>
-      <c r="D127" s="54"/>
-      <c r="E127" s="54"/>
-      <c r="F127" s="54"/>
-      <c r="G127" s="54"/>
-      <c r="H127" s="54"/>
-      <c r="I127" s="54"/>
-      <c r="J127" s="54"/>
-      <c r="K127" s="55"/>
+      <c r="B127" s="25"/>
+      <c r="C127" s="47"/>
+      <c r="D127" s="47"/>
+      <c r="E127" s="47"/>
+      <c r="F127" s="47"/>
+      <c r="G127" s="47"/>
+      <c r="H127" s="47"/>
+      <c r="I127" s="47"/>
+      <c r="J127" s="47"/>
+      <c r="K127" s="48"/>
     </row>
     <row r="128" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B128" s="56"/>
-      <c r="C128" s="57"/>
-      <c r="D128" s="57"/>
-      <c r="E128" s="57"/>
-      <c r="F128" s="57"/>
-      <c r="G128" s="57"/>
-      <c r="H128" s="57"/>
-      <c r="I128" s="57"/>
-      <c r="J128" s="57"/>
-      <c r="K128" s="58"/>
+      <c r="B128" s="49"/>
+      <c r="C128" s="50"/>
+      <c r="D128" s="50"/>
+      <c r="E128" s="50"/>
+      <c r="F128" s="50"/>
+      <c r="G128" s="50"/>
+      <c r="H128" s="50"/>
+      <c r="I128" s="50"/>
+      <c r="J128" s="50"/>
+      <c r="K128" s="51"/>
     </row>
     <row r="129" spans="2:13" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B129" s="42" t="s">
+      <c r="B129" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C129" s="43"/>
-      <c r="D129" s="59" t="s">
+      <c r="C129" s="33"/>
+      <c r="D129" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="E129" s="59"/>
-      <c r="F129" s="60"/>
-      <c r="G129" s="61" t="s">
+      <c r="E129" s="52"/>
+      <c r="F129" s="53"/>
+      <c r="G129" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="H129" s="62"/>
-      <c r="I129" s="63" t="s">
+      <c r="H129" s="55"/>
+      <c r="I129" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="J129" s="63"/>
-      <c r="K129" s="64"/>
+      <c r="J129" s="56"/>
+      <c r="K129" s="57"/>
     </row>
     <row r="130" spans="2:13" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B130" s="42" t="s">
+      <c r="B130" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C130" s="43"/>
-      <c r="D130" s="43"/>
-      <c r="E130" s="43"/>
-      <c r="F130" s="43"/>
-      <c r="G130" s="43"/>
-      <c r="H130" s="43"/>
-      <c r="I130" s="43"/>
-      <c r="J130" s="43"/>
-      <c r="K130" s="44"/>
+      <c r="C130" s="33"/>
+      <c r="D130" s="33"/>
+      <c r="E130" s="33"/>
+      <c r="F130" s="33"/>
+      <c r="G130" s="33"/>
+      <c r="H130" s="33"/>
+      <c r="I130" s="33"/>
+      <c r="J130" s="33"/>
+      <c r="K130" s="34"/>
     </row>
     <row r="131" spans="2:13" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B131" s="45" t="s">
+      <c r="B131" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C131" s="65"/>
-      <c r="D131" s="65"/>
-      <c r="E131" s="65"/>
-      <c r="F131" s="65"/>
-      <c r="G131" s="65"/>
-      <c r="H131" s="65"/>
-      <c r="I131" s="65"/>
-      <c r="J131" s="65"/>
-      <c r="K131" s="66"/>
+      <c r="C131" s="58"/>
+      <c r="D131" s="58"/>
+      <c r="E131" s="58"/>
+      <c r="F131" s="58"/>
+      <c r="G131" s="58"/>
+      <c r="H131" s="58"/>
+      <c r="I131" s="58"/>
+      <c r="J131" s="58"/>
+      <c r="K131" s="59"/>
     </row>
     <row r="132" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B132" s="30" t="s">
+      <c r="B132" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C132" s="31"/>
-      <c r="D132" s="31" t="s">
+      <c r="C132" s="21"/>
+      <c r="D132" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E132" s="31"/>
-      <c r="F132" s="31"/>
-      <c r="G132" s="31"/>
-      <c r="H132" s="31"/>
-      <c r="I132" s="31"/>
-      <c r="J132" s="31" t="s">
+      <c r="E132" s="21"/>
+      <c r="F132" s="21"/>
+      <c r="G132" s="21"/>
+      <c r="H132" s="21"/>
+      <c r="I132" s="21"/>
+      <c r="J132" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K132" s="32"/>
+      <c r="K132" s="22"/>
     </row>
     <row r="133" spans="2:13" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B133" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="33"/>
-      <c r="D133" s="33"/>
-      <c r="E133" s="33"/>
-      <c r="F133" s="33"/>
-      <c r="G133" s="33"/>
-      <c r="H133" s="33"/>
-      <c r="I133" s="33"/>
-      <c r="J133" s="33"/>
-      <c r="K133" s="34"/>
+      <c r="C133" s="23"/>
+      <c r="D133" s="23"/>
+      <c r="E133" s="23"/>
+      <c r="F133" s="23"/>
+      <c r="G133" s="23"/>
+      <c r="H133" s="23"/>
+      <c r="I133" s="23"/>
+      <c r="J133" s="23"/>
+      <c r="K133" s="24"/>
     </row>
     <row r="134" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B134" s="30" t="s">
+      <c r="B134" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C134" s="31"/>
-      <c r="D134" s="31" t="s">
+      <c r="C134" s="21"/>
+      <c r="D134" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="31"/>
-      <c r="F134" s="31" t="s">
+      <c r="E134" s="21"/>
+      <c r="F134" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G134" s="31"/>
-      <c r="H134" s="31"/>
-      <c r="I134" s="31"/>
-      <c r="J134" s="31" t="s">
+      <c r="G134" s="21"/>
+      <c r="H134" s="21"/>
+      <c r="I134" s="21"/>
+      <c r="J134" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K134" s="32"/>
+      <c r="K134" s="22"/>
     </row>
     <row r="135" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B135" s="26" t="s">
+      <c r="B135" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C135" s="23"/>
-      <c r="D135" s="23" t="s">
+      <c r="C135" s="17"/>
+      <c r="D135" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E135" s="23"/>
-      <c r="F135" s="25" t="s">
+      <c r="E135" s="17"/>
+      <c r="F135" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G135" s="23"/>
-      <c r="H135" s="23"/>
-      <c r="I135" s="23"/>
-      <c r="J135" s="23" t="s">
+      <c r="G135" s="17"/>
+      <c r="H135" s="17"/>
+      <c r="I135" s="17"/>
+      <c r="J135" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="K135" s="24"/>
+      <c r="K135" s="19"/>
     </row>
     <row r="136" spans="2:13" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B136" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C136" s="33"/>
-      <c r="D136" s="33"/>
-      <c r="E136" s="33"/>
-      <c r="F136" s="33"/>
-      <c r="G136" s="33"/>
-      <c r="H136" s="33"/>
-      <c r="I136" s="33"/>
-      <c r="J136" s="33"/>
-      <c r="K136" s="34"/>
+      <c r="C136" s="23"/>
+      <c r="D136" s="23"/>
+      <c r="E136" s="23"/>
+      <c r="F136" s="23"/>
+      <c r="G136" s="23"/>
+      <c r="H136" s="23"/>
+      <c r="I136" s="23"/>
+      <c r="J136" s="23"/>
+      <c r="K136" s="24"/>
     </row>
     <row r="137" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B137" s="35" t="s">
+      <c r="B137" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C137" s="36"/>
-      <c r="D137" s="36"/>
-      <c r="E137" s="36"/>
-      <c r="F137" s="36"/>
-      <c r="G137" s="36"/>
-      <c r="H137" s="36"/>
-      <c r="I137" s="36"/>
-      <c r="J137" s="36"/>
-      <c r="K137" s="37"/>
+      <c r="C137" s="26"/>
+      <c r="D137" s="26"/>
+      <c r="E137" s="26"/>
+      <c r="F137" s="26"/>
+      <c r="G137" s="26"/>
+      <c r="H137" s="26"/>
+      <c r="I137" s="26"/>
+      <c r="J137" s="26"/>
+      <c r="K137" s="27"/>
     </row>
     <row r="138" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B138" s="38"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-      <c r="G138" s="36"/>
-      <c r="H138" s="36"/>
-      <c r="I138" s="36"/>
-      <c r="J138" s="36"/>
-      <c r="K138" s="37"/>
+      <c r="B138" s="28"/>
+      <c r="C138" s="26"/>
+      <c r="D138" s="26"/>
+      <c r="E138" s="26"/>
+      <c r="F138" s="26"/>
+      <c r="G138" s="26"/>
+      <c r="H138" s="26"/>
+      <c r="I138" s="26"/>
+      <c r="J138" s="26"/>
+      <c r="K138" s="27"/>
     </row>
     <row r="139" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B139" s="38"/>
-      <c r="C139" s="36"/>
-      <c r="D139" s="36"/>
-      <c r="E139" s="36"/>
-      <c r="F139" s="36"/>
-      <c r="G139" s="36"/>
-      <c r="H139" s="36"/>
-      <c r="I139" s="36"/>
-      <c r="J139" s="36"/>
-      <c r="K139" s="37"/>
+      <c r="B139" s="28"/>
+      <c r="C139" s="26"/>
+      <c r="D139" s="26"/>
+      <c r="E139" s="26"/>
+      <c r="F139" s="26"/>
+      <c r="G139" s="26"/>
+      <c r="H139" s="26"/>
+      <c r="I139" s="26"/>
+      <c r="J139" s="26"/>
+      <c r="K139" s="27"/>
       <c r="M139" s="4"/>
     </row>
     <row r="140" spans="2:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B140" s="39"/>
-      <c r="C140" s="40"/>
-      <c r="D140" s="40"/>
-      <c r="E140" s="40"/>
-      <c r="F140" s="40"/>
-      <c r="G140" s="40"/>
-      <c r="H140" s="40"/>
-      <c r="I140" s="40"/>
-      <c r="J140" s="40"/>
-      <c r="K140" s="41"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="30"/>
+      <c r="D140" s="30"/>
+      <c r="E140" s="30"/>
+      <c r="F140" s="30"/>
+      <c r="G140" s="30"/>
+      <c r="H140" s="30"/>
+      <c r="I140" s="30"/>
+      <c r="J140" s="30"/>
+      <c r="K140" s="31"/>
     </row>
     <row r="141" spans="2:13" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B141" s="42" t="s">
+      <c r="B141" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C141" s="43"/>
-      <c r="D141" s="43"/>
-      <c r="E141" s="43"/>
-      <c r="F141" s="43"/>
-      <c r="G141" s="43"/>
-      <c r="H141" s="43"/>
-      <c r="I141" s="43"/>
-      <c r="J141" s="43"/>
-      <c r="K141" s="44"/>
+      <c r="C141" s="33"/>
+      <c r="D141" s="33"/>
+      <c r="E141" s="33"/>
+      <c r="F141" s="33"/>
+      <c r="G141" s="33"/>
+      <c r="H141" s="33"/>
+      <c r="I141" s="33"/>
+      <c r="J141" s="33"/>
+      <c r="K141" s="34"/>
     </row>
     <row r="142" spans="2:13" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B142" s="45" t="s">
+      <c r="B142" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C142" s="46"/>
-      <c r="D142" s="46"/>
-      <c r="E142" s="46"/>
-      <c r="F142" s="46"/>
-      <c r="G142" s="46"/>
-      <c r="H142" s="46"/>
-      <c r="I142" s="46"/>
-      <c r="J142" s="46"/>
-      <c r="K142" s="47"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+      <c r="G142" s="36"/>
+      <c r="H142" s="36"/>
+      <c r="I142" s="36"/>
+      <c r="J142" s="36"/>
+      <c r="K142" s="37"/>
     </row>
     <row r="143" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B143" s="30" t="s">
+      <c r="B143" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C143" s="31"/>
-      <c r="D143" s="31" t="s">
+      <c r="C143" s="21"/>
+      <c r="D143" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E143" s="31"/>
-      <c r="F143" s="31"/>
-      <c r="G143" s="31"/>
-      <c r="H143" s="31"/>
-      <c r="I143" s="31"/>
-      <c r="J143" s="31" t="s">
+      <c r="E143" s="21"/>
+      <c r="F143" s="21"/>
+      <c r="G143" s="21"/>
+      <c r="H143" s="21"/>
+      <c r="I143" s="21"/>
+      <c r="J143" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K143" s="32"/>
+      <c r="K143" s="22"/>
     </row>
     <row r="144" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B144" s="27" t="s">
+      <c r="B144" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C144" s="28"/>
-      <c r="D144" s="28" t="s">
+      <c r="C144" s="39"/>
+      <c r="D144" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E144" s="28"/>
-      <c r="F144" s="28"/>
-      <c r="G144" s="28"/>
-      <c r="H144" s="28"/>
-      <c r="I144" s="28"/>
-      <c r="J144" s="28" t="s">
+      <c r="E144" s="39"/>
+      <c r="F144" s="39"/>
+      <c r="G144" s="39"/>
+      <c r="H144" s="39"/>
+      <c r="I144" s="39"/>
+      <c r="J144" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="K144" s="29"/>
+      <c r="K144" s="40"/>
     </row>
     <row r="145" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B145" s="10" t="s">
@@ -3917,24 +3913,24 @@
       <c r="K145" s="12"/>
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B146" s="30" t="s">
+      <c r="B146" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C146" s="31"/>
-      <c r="D146" s="31" t="s">
+      <c r="C146" s="21"/>
+      <c r="D146" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E146" s="31"/>
-      <c r="F146" s="31" t="s">
+      <c r="E146" s="21"/>
+      <c r="F146" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G146" s="31"/>
-      <c r="H146" s="31"/>
-      <c r="I146" s="31"/>
-      <c r="J146" s="31" t="s">
+      <c r="G146" s="21"/>
+      <c r="H146" s="21"/>
+      <c r="I146" s="21"/>
+      <c r="J146" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K146" s="32"/>
+      <c r="K146" s="22"/>
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B147" s="5" t="s">
@@ -4006,350 +4002,350 @@
     </row>
     <row r="151" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="152" spans="2:11" ht="41.25" x14ac:dyDescent="0.3">
-      <c r="B152" s="48" t="s">
+      <c r="B152" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="C152" s="49"/>
-      <c r="D152" s="49"/>
-      <c r="E152" s="49"/>
-      <c r="F152" s="49"/>
-      <c r="G152" s="49"/>
-      <c r="H152" s="49"/>
-      <c r="I152" s="49"/>
-      <c r="J152" s="49"/>
-      <c r="K152" s="50"/>
+      <c r="C152" s="42"/>
+      <c r="D152" s="42"/>
+      <c r="E152" s="42"/>
+      <c r="F152" s="42"/>
+      <c r="G152" s="42"/>
+      <c r="H152" s="42"/>
+      <c r="I152" s="42"/>
+      <c r="J152" s="42"/>
+      <c r="K152" s="43"/>
     </row>
     <row r="153" spans="2:11" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="B153" s="51" t="s">
+      <c r="B153" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C153" s="52"/>
-      <c r="D153" s="52"/>
-      <c r="E153" s="52"/>
-      <c r="F153" s="52"/>
-      <c r="G153" s="52"/>
-      <c r="H153" s="52"/>
-      <c r="I153" s="52"/>
-      <c r="J153" s="52"/>
-      <c r="K153" s="53"/>
+      <c r="C153" s="45"/>
+      <c r="D153" s="45"/>
+      <c r="E153" s="45"/>
+      <c r="F153" s="45"/>
+      <c r="G153" s="45"/>
+      <c r="H153" s="45"/>
+      <c r="I153" s="45"/>
+      <c r="J153" s="45"/>
+      <c r="K153" s="46"/>
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B154" s="35" t="s">
+      <c r="B154" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C154" s="54"/>
-      <c r="D154" s="54"/>
-      <c r="E154" s="54"/>
-      <c r="F154" s="54"/>
-      <c r="G154" s="54"/>
-      <c r="H154" s="54"/>
-      <c r="I154" s="54"/>
-      <c r="J154" s="54"/>
-      <c r="K154" s="55"/>
+      <c r="C154" s="47"/>
+      <c r="D154" s="47"/>
+      <c r="E154" s="47"/>
+      <c r="F154" s="47"/>
+      <c r="G154" s="47"/>
+      <c r="H154" s="47"/>
+      <c r="I154" s="47"/>
+      <c r="J154" s="47"/>
+      <c r="K154" s="48"/>
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B155" s="35"/>
-      <c r="C155" s="54"/>
-      <c r="D155" s="54"/>
-      <c r="E155" s="54"/>
-      <c r="F155" s="54"/>
-      <c r="G155" s="54"/>
-      <c r="H155" s="54"/>
-      <c r="I155" s="54"/>
-      <c r="J155" s="54"/>
-      <c r="K155" s="55"/>
+      <c r="B155" s="25"/>
+      <c r="C155" s="47"/>
+      <c r="D155" s="47"/>
+      <c r="E155" s="47"/>
+      <c r="F155" s="47"/>
+      <c r="G155" s="47"/>
+      <c r="H155" s="47"/>
+      <c r="I155" s="47"/>
+      <c r="J155" s="47"/>
+      <c r="K155" s="48"/>
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B156" s="35"/>
-      <c r="C156" s="54"/>
-      <c r="D156" s="54"/>
-      <c r="E156" s="54"/>
-      <c r="F156" s="54"/>
-      <c r="G156" s="54"/>
-      <c r="H156" s="54"/>
-      <c r="I156" s="54"/>
-      <c r="J156" s="54"/>
-      <c r="K156" s="55"/>
+      <c r="B156" s="25"/>
+      <c r="C156" s="47"/>
+      <c r="D156" s="47"/>
+      <c r="E156" s="47"/>
+      <c r="F156" s="47"/>
+      <c r="G156" s="47"/>
+      <c r="H156" s="47"/>
+      <c r="I156" s="47"/>
+      <c r="J156" s="47"/>
+      <c r="K156" s="48"/>
     </row>
     <row r="157" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="56"/>
-      <c r="C157" s="57"/>
-      <c r="D157" s="57"/>
-      <c r="E157" s="57"/>
-      <c r="F157" s="57"/>
-      <c r="G157" s="57"/>
-      <c r="H157" s="57"/>
-      <c r="I157" s="57"/>
-      <c r="J157" s="57"/>
-      <c r="K157" s="58"/>
+      <c r="B157" s="49"/>
+      <c r="C157" s="50"/>
+      <c r="D157" s="50"/>
+      <c r="E157" s="50"/>
+      <c r="F157" s="50"/>
+      <c r="G157" s="50"/>
+      <c r="H157" s="50"/>
+      <c r="I157" s="50"/>
+      <c r="J157" s="50"/>
+      <c r="K157" s="51"/>
     </row>
     <row r="158" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B158" s="42" t="s">
+      <c r="B158" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C158" s="43"/>
-      <c r="D158" s="59" t="s">
+      <c r="C158" s="33"/>
+      <c r="D158" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="E158" s="59"/>
-      <c r="F158" s="60"/>
-      <c r="G158" s="61" t="s">
+      <c r="E158" s="52"/>
+      <c r="F158" s="53"/>
+      <c r="G158" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="H158" s="62"/>
-      <c r="I158" s="63" t="s">
+      <c r="H158" s="55"/>
+      <c r="I158" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="J158" s="63"/>
-      <c r="K158" s="64"/>
+      <c r="J158" s="56"/>
+      <c r="K158" s="57"/>
     </row>
     <row r="159" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B159" s="42" t="s">
+      <c r="B159" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C159" s="43"/>
-      <c r="D159" s="43"/>
-      <c r="E159" s="43"/>
-      <c r="F159" s="43"/>
-      <c r="G159" s="43"/>
-      <c r="H159" s="43"/>
-      <c r="I159" s="43"/>
-      <c r="J159" s="43"/>
-      <c r="K159" s="44"/>
+      <c r="C159" s="33"/>
+      <c r="D159" s="33"/>
+      <c r="E159" s="33"/>
+      <c r="F159" s="33"/>
+      <c r="G159" s="33"/>
+      <c r="H159" s="33"/>
+      <c r="I159" s="33"/>
+      <c r="J159" s="33"/>
+      <c r="K159" s="34"/>
     </row>
     <row r="160" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B160" s="45" t="s">
+      <c r="B160" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C160" s="65"/>
-      <c r="D160" s="65"/>
-      <c r="E160" s="65"/>
-      <c r="F160" s="65"/>
-      <c r="G160" s="65"/>
-      <c r="H160" s="65"/>
-      <c r="I160" s="65"/>
-      <c r="J160" s="65"/>
-      <c r="K160" s="66"/>
+      <c r="C160" s="58"/>
+      <c r="D160" s="58"/>
+      <c r="E160" s="58"/>
+      <c r="F160" s="58"/>
+      <c r="G160" s="58"/>
+      <c r="H160" s="58"/>
+      <c r="I160" s="58"/>
+      <c r="J160" s="58"/>
+      <c r="K160" s="59"/>
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B161" s="30" t="s">
+      <c r="B161" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C161" s="31"/>
-      <c r="D161" s="31" t="s">
+      <c r="C161" s="21"/>
+      <c r="D161" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E161" s="31"/>
-      <c r="F161" s="31"/>
-      <c r="G161" s="31"/>
-      <c r="H161" s="31"/>
-      <c r="I161" s="31"/>
-      <c r="J161" s="31" t="s">
+      <c r="E161" s="21"/>
+      <c r="F161" s="21"/>
+      <c r="G161" s="21"/>
+      <c r="H161" s="21"/>
+      <c r="I161" s="21"/>
+      <c r="J161" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K161" s="32"/>
+      <c r="K161" s="22"/>
     </row>
     <row r="162" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B162" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C162" s="33"/>
-      <c r="D162" s="33"/>
-      <c r="E162" s="33"/>
-      <c r="F162" s="33"/>
-      <c r="G162" s="33"/>
-      <c r="H162" s="33"/>
-      <c r="I162" s="33"/>
-      <c r="J162" s="33"/>
-      <c r="K162" s="34"/>
+      <c r="C162" s="23"/>
+      <c r="D162" s="23"/>
+      <c r="E162" s="23"/>
+      <c r="F162" s="23"/>
+      <c r="G162" s="23"/>
+      <c r="H162" s="23"/>
+      <c r="I162" s="23"/>
+      <c r="J162" s="23"/>
+      <c r="K162" s="24"/>
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B163" s="30" t="s">
+      <c r="B163" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C163" s="31"/>
-      <c r="D163" s="31" t="s">
+      <c r="C163" s="21"/>
+      <c r="D163" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="31"/>
-      <c r="F163" s="31" t="s">
+      <c r="E163" s="21"/>
+      <c r="F163" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G163" s="31"/>
-      <c r="H163" s="31"/>
-      <c r="I163" s="31"/>
-      <c r="J163" s="31" t="s">
+      <c r="G163" s="21"/>
+      <c r="H163" s="21"/>
+      <c r="I163" s="21"/>
+      <c r="J163" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K163" s="32"/>
+      <c r="K163" s="22"/>
     </row>
     <row r="164" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B164" s="26" t="s">
+      <c r="B164" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C164" s="23"/>
-      <c r="D164" s="23" t="s">
+      <c r="C164" s="17"/>
+      <c r="D164" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E164" s="23"/>
-      <c r="F164" s="25" t="s">
+      <c r="E164" s="17"/>
+      <c r="F164" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G164" s="23"/>
-      <c r="H164" s="23"/>
-      <c r="I164" s="23"/>
-      <c r="J164" s="23" t="s">
+      <c r="G164" s="17"/>
+      <c r="H164" s="17"/>
+      <c r="I164" s="17"/>
+      <c r="J164" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K164" s="24"/>
+      <c r="K164" s="19"/>
     </row>
     <row r="165" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B165" s="26" t="s">
+      <c r="B165" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C165" s="23"/>
-      <c r="D165" s="23" t="s">
+      <c r="C165" s="17"/>
+      <c r="D165" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="E165" s="23"/>
-      <c r="F165" s="25" t="s">
+      <c r="E165" s="17"/>
+      <c r="F165" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G165" s="25"/>
-      <c r="H165" s="25"/>
-      <c r="I165" s="25"/>
-      <c r="J165" s="23" t="s">
+      <c r="G165" s="18"/>
+      <c r="H165" s="18"/>
+      <c r="I165" s="18"/>
+      <c r="J165" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K165" s="24"/>
+      <c r="K165" s="19"/>
     </row>
     <row r="166" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B166" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C166" s="33"/>
-      <c r="D166" s="33"/>
-      <c r="E166" s="33"/>
-      <c r="F166" s="33"/>
-      <c r="G166" s="33"/>
-      <c r="H166" s="33"/>
-      <c r="I166" s="33"/>
-      <c r="J166" s="33"/>
-      <c r="K166" s="34"/>
+      <c r="C166" s="23"/>
+      <c r="D166" s="23"/>
+      <c r="E166" s="23"/>
+      <c r="F166" s="23"/>
+      <c r="G166" s="23"/>
+      <c r="H166" s="23"/>
+      <c r="I166" s="23"/>
+      <c r="J166" s="23"/>
+      <c r="K166" s="24"/>
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B167" s="35" t="s">
+      <c r="B167" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-      <c r="G167" s="36"/>
-      <c r="H167" s="36"/>
-      <c r="I167" s="36"/>
-      <c r="J167" s="36"/>
-      <c r="K167" s="37"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="F167" s="26"/>
+      <c r="G167" s="26"/>
+      <c r="H167" s="26"/>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+      <c r="K167" s="27"/>
     </row>
     <row r="168" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B168" s="38"/>
-      <c r="C168" s="36"/>
-      <c r="D168" s="36"/>
-      <c r="E168" s="36"/>
-      <c r="F168" s="36"/>
-      <c r="G168" s="36"/>
-      <c r="H168" s="36"/>
-      <c r="I168" s="36"/>
-      <c r="J168" s="36"/>
-      <c r="K168" s="37"/>
+      <c r="B168" s="28"/>
+      <c r="C168" s="26"/>
+      <c r="D168" s="26"/>
+      <c r="E168" s="26"/>
+      <c r="F168" s="26"/>
+      <c r="G168" s="26"/>
+      <c r="H168" s="26"/>
+      <c r="I168" s="26"/>
+      <c r="J168" s="26"/>
+      <c r="K168" s="27"/>
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B169" s="38"/>
-      <c r="C169" s="36"/>
-      <c r="D169" s="36"/>
-      <c r="E169" s="36"/>
-      <c r="F169" s="36"/>
-      <c r="G169" s="36"/>
-      <c r="H169" s="36"/>
-      <c r="I169" s="36"/>
-      <c r="J169" s="36"/>
-      <c r="K169" s="37"/>
+      <c r="B169" s="28"/>
+      <c r="C169" s="26"/>
+      <c r="D169" s="26"/>
+      <c r="E169" s="26"/>
+      <c r="F169" s="26"/>
+      <c r="G169" s="26"/>
+      <c r="H169" s="26"/>
+      <c r="I169" s="26"/>
+      <c r="J169" s="26"/>
+      <c r="K169" s="27"/>
     </row>
     <row r="170" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B170" s="39"/>
-      <c r="C170" s="40"/>
-      <c r="D170" s="40"/>
-      <c r="E170" s="40"/>
-      <c r="F170" s="40"/>
-      <c r="G170" s="40"/>
-      <c r="H170" s="40"/>
-      <c r="I170" s="40"/>
-      <c r="J170" s="40"/>
-      <c r="K170" s="41"/>
+      <c r="B170" s="29"/>
+      <c r="C170" s="30"/>
+      <c r="D170" s="30"/>
+      <c r="E170" s="30"/>
+      <c r="F170" s="30"/>
+      <c r="G170" s="30"/>
+      <c r="H170" s="30"/>
+      <c r="I170" s="30"/>
+      <c r="J170" s="30"/>
+      <c r="K170" s="31"/>
     </row>
     <row r="171" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B171" s="42" t="s">
+      <c r="B171" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="C171" s="43"/>
-      <c r="D171" s="43"/>
-      <c r="E171" s="43"/>
-      <c r="F171" s="43"/>
-      <c r="G171" s="43"/>
-      <c r="H171" s="43"/>
-      <c r="I171" s="43"/>
-      <c r="J171" s="43"/>
-      <c r="K171" s="44"/>
+      <c r="C171" s="33"/>
+      <c r="D171" s="33"/>
+      <c r="E171" s="33"/>
+      <c r="F171" s="33"/>
+      <c r="G171" s="33"/>
+      <c r="H171" s="33"/>
+      <c r="I171" s="33"/>
+      <c r="J171" s="33"/>
+      <c r="K171" s="34"/>
     </row>
     <row r="172" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B172" s="45" t="s">
+      <c r="B172" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C172" s="46"/>
-      <c r="D172" s="46"/>
-      <c r="E172" s="46"/>
-      <c r="F172" s="46"/>
-      <c r="G172" s="46"/>
-      <c r="H172" s="46"/>
-      <c r="I172" s="46"/>
-      <c r="J172" s="46"/>
-      <c r="K172" s="47"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+      <c r="G172" s="36"/>
+      <c r="H172" s="36"/>
+      <c r="I172" s="36"/>
+      <c r="J172" s="36"/>
+      <c r="K172" s="37"/>
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B173" s="30" t="s">
+      <c r="B173" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C173" s="31"/>
-      <c r="D173" s="31" t="s">
+      <c r="C173" s="21"/>
+      <c r="D173" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E173" s="31"/>
-      <c r="F173" s="31"/>
-      <c r="G173" s="31"/>
-      <c r="H173" s="31"/>
-      <c r="I173" s="31"/>
-      <c r="J173" s="31" t="s">
+      <c r="E173" s="21"/>
+      <c r="F173" s="21"/>
+      <c r="G173" s="21"/>
+      <c r="H173" s="21"/>
+      <c r="I173" s="21"/>
+      <c r="J173" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K173" s="32"/>
+      <c r="K173" s="22"/>
     </row>
     <row r="174" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B174" s="27" t="s">
+      <c r="B174" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C174" s="28"/>
-      <c r="D174" s="28" t="s">
+      <c r="C174" s="39"/>
+      <c r="D174" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E174" s="28"/>
-      <c r="F174" s="28"/>
-      <c r="G174" s="28"/>
-      <c r="H174" s="28"/>
-      <c r="I174" s="28"/>
-      <c r="J174" s="28" t="s">
+      <c r="E174" s="39"/>
+      <c r="F174" s="39"/>
+      <c r="G174" s="39"/>
+      <c r="H174" s="39"/>
+      <c r="I174" s="39"/>
+      <c r="J174" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="K174" s="29"/>
+      <c r="K174" s="40"/>
     </row>
     <row r="175" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B175" s="10" t="s">
@@ -4366,24 +4362,24 @@
       <c r="K175" s="12"/>
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B176" s="30" t="s">
+      <c r="B176" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C176" s="31"/>
-      <c r="D176" s="31" t="s">
+      <c r="C176" s="21"/>
+      <c r="D176" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="31"/>
-      <c r="F176" s="31" t="s">
+      <c r="E176" s="21"/>
+      <c r="F176" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G176" s="31"/>
-      <c r="H176" s="31"/>
-      <c r="I176" s="31"/>
-      <c r="J176" s="31" t="s">
+      <c r="G176" s="21"/>
+      <c r="H176" s="21"/>
+      <c r="I176" s="21"/>
+      <c r="J176" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K176" s="32"/>
+      <c r="K176" s="22"/>
     </row>
     <row r="177" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B177" s="5" t="s">
@@ -4455,390 +4451,390 @@
     </row>
     <row r="181" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="182" spans="2:11" ht="41.25" x14ac:dyDescent="0.3">
-      <c r="B182" s="48" t="s">
+      <c r="B182" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="C182" s="49"/>
-      <c r="D182" s="49"/>
-      <c r="E182" s="49"/>
-      <c r="F182" s="49"/>
-      <c r="G182" s="49"/>
-      <c r="H182" s="49"/>
-      <c r="I182" s="49"/>
-      <c r="J182" s="49"/>
-      <c r="K182" s="50"/>
+      <c r="C182" s="42"/>
+      <c r="D182" s="42"/>
+      <c r="E182" s="42"/>
+      <c r="F182" s="42"/>
+      <c r="G182" s="42"/>
+      <c r="H182" s="42"/>
+      <c r="I182" s="42"/>
+      <c r="J182" s="42"/>
+      <c r="K182" s="43"/>
     </row>
     <row r="183" spans="2:11" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="B183" s="51" t="s">
+      <c r="B183" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C183" s="52"/>
-      <c r="D183" s="52"/>
-      <c r="E183" s="52"/>
-      <c r="F183" s="52"/>
-      <c r="G183" s="52"/>
-      <c r="H183" s="52"/>
-      <c r="I183" s="52"/>
-      <c r="J183" s="52"/>
-      <c r="K183" s="53"/>
+      <c r="C183" s="45"/>
+      <c r="D183" s="45"/>
+      <c r="E183" s="45"/>
+      <c r="F183" s="45"/>
+      <c r="G183" s="45"/>
+      <c r="H183" s="45"/>
+      <c r="I183" s="45"/>
+      <c r="J183" s="45"/>
+      <c r="K183" s="46"/>
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B184" s="35" t="s">
+      <c r="B184" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C184" s="47"/>
+      <c r="D184" s="47"/>
+      <c r="E184" s="47"/>
+      <c r="F184" s="47"/>
+      <c r="G184" s="47"/>
+      <c r="H184" s="47"/>
+      <c r="I184" s="47"/>
+      <c r="J184" s="47"/>
+      <c r="K184" s="48"/>
+    </row>
+    <row r="185" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B185" s="25"/>
+      <c r="C185" s="47"/>
+      <c r="D185" s="47"/>
+      <c r="E185" s="47"/>
+      <c r="F185" s="47"/>
+      <c r="G185" s="47"/>
+      <c r="H185" s="47"/>
+      <c r="I185" s="47"/>
+      <c r="J185" s="47"/>
+      <c r="K185" s="48"/>
+    </row>
+    <row r="186" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B186" s="25"/>
+      <c r="C186" s="47"/>
+      <c r="D186" s="47"/>
+      <c r="E186" s="47"/>
+      <c r="F186" s="47"/>
+      <c r="G186" s="47"/>
+      <c r="H186" s="47"/>
+      <c r="I186" s="47"/>
+      <c r="J186" s="47"/>
+      <c r="K186" s="48"/>
+    </row>
+    <row r="187" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B187" s="49"/>
+      <c r="C187" s="50"/>
+      <c r="D187" s="50"/>
+      <c r="E187" s="50"/>
+      <c r="F187" s="50"/>
+      <c r="G187" s="50"/>
+      <c r="H187" s="50"/>
+      <c r="I187" s="50"/>
+      <c r="J187" s="50"/>
+      <c r="K187" s="51"/>
+    </row>
+    <row r="188" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B188" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C188" s="33"/>
+      <c r="D188" s="52" t="s">
+        <v>89</v>
+      </c>
+      <c r="E188" s="52"/>
+      <c r="F188" s="53"/>
+      <c r="G188" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="H188" s="55"/>
+      <c r="I188" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="C184" s="54"/>
-      <c r="D184" s="54"/>
-      <c r="E184" s="54"/>
-      <c r="F184" s="54"/>
-      <c r="G184" s="54"/>
-      <c r="H184" s="54"/>
-      <c r="I184" s="54"/>
-      <c r="J184" s="54"/>
-      <c r="K184" s="55"/>
-    </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B185" s="35"/>
-      <c r="C185" s="54"/>
-      <c r="D185" s="54"/>
-      <c r="E185" s="54"/>
-      <c r="F185" s="54"/>
-      <c r="G185" s="54"/>
-      <c r="H185" s="54"/>
-      <c r="I185" s="54"/>
-      <c r="J185" s="54"/>
-      <c r="K185" s="55"/>
-    </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B186" s="35"/>
-      <c r="C186" s="54"/>
-      <c r="D186" s="54"/>
-      <c r="E186" s="54"/>
-      <c r="F186" s="54"/>
-      <c r="G186" s="54"/>
-      <c r="H186" s="54"/>
-      <c r="I186" s="54"/>
-      <c r="J186" s="54"/>
-      <c r="K186" s="55"/>
-    </row>
-    <row r="187" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B187" s="56"/>
-      <c r="C187" s="57"/>
-      <c r="D187" s="57"/>
-      <c r="E187" s="57"/>
-      <c r="F187" s="57"/>
-      <c r="G187" s="57"/>
-      <c r="H187" s="57"/>
-      <c r="I187" s="57"/>
-      <c r="J187" s="57"/>
-      <c r="K187" s="58"/>
-    </row>
-    <row r="188" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B188" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="C188" s="43"/>
-      <c r="D188" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="E188" s="59"/>
-      <c r="F188" s="60"/>
-      <c r="G188" s="61" t="s">
-        <v>5</v>
-      </c>
-      <c r="H188" s="62"/>
-      <c r="I188" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="J188" s="63"/>
-      <c r="K188" s="64"/>
+      <c r="J188" s="56"/>
+      <c r="K188" s="57"/>
     </row>
     <row r="189" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B189" s="42" t="s">
+      <c r="B189" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C189" s="43"/>
-      <c r="D189" s="43"/>
-      <c r="E189" s="43"/>
-      <c r="F189" s="43"/>
-      <c r="G189" s="43"/>
-      <c r="H189" s="43"/>
-      <c r="I189" s="43"/>
-      <c r="J189" s="43"/>
-      <c r="K189" s="44"/>
+      <c r="C189" s="33"/>
+      <c r="D189" s="33"/>
+      <c r="E189" s="33"/>
+      <c r="F189" s="33"/>
+      <c r="G189" s="33"/>
+      <c r="H189" s="33"/>
+      <c r="I189" s="33"/>
+      <c r="J189" s="33"/>
+      <c r="K189" s="34"/>
     </row>
     <row r="190" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B190" s="45" t="s">
+      <c r="B190" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C190" s="65"/>
-      <c r="D190" s="65"/>
-      <c r="E190" s="65"/>
-      <c r="F190" s="65"/>
-      <c r="G190" s="65"/>
-      <c r="H190" s="65"/>
-      <c r="I190" s="65"/>
-      <c r="J190" s="65"/>
-      <c r="K190" s="66"/>
+      <c r="C190" s="58"/>
+      <c r="D190" s="58"/>
+      <c r="E190" s="58"/>
+      <c r="F190" s="58"/>
+      <c r="G190" s="58"/>
+      <c r="H190" s="58"/>
+      <c r="I190" s="58"/>
+      <c r="J190" s="58"/>
+      <c r="K190" s="59"/>
     </row>
     <row r="191" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B191" s="30" t="s">
+      <c r="B191" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C191" s="31"/>
-      <c r="D191" s="31" t="s">
+      <c r="C191" s="21"/>
+      <c r="D191" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E191" s="31"/>
-      <c r="F191" s="31"/>
-      <c r="G191" s="31"/>
-      <c r="H191" s="31"/>
-      <c r="I191" s="31"/>
-      <c r="J191" s="31" t="s">
+      <c r="E191" s="21"/>
+      <c r="F191" s="21"/>
+      <c r="G191" s="21"/>
+      <c r="H191" s="21"/>
+      <c r="I191" s="21"/>
+      <c r="J191" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K191" s="32"/>
+      <c r="K191" s="22"/>
     </row>
     <row r="192" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B192" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C192" s="33"/>
-      <c r="D192" s="33"/>
-      <c r="E192" s="33"/>
-      <c r="F192" s="33"/>
-      <c r="G192" s="33"/>
-      <c r="H192" s="33"/>
-      <c r="I192" s="33"/>
-      <c r="J192" s="33"/>
-      <c r="K192" s="34"/>
+      <c r="C192" s="23"/>
+      <c r="D192" s="23"/>
+      <c r="E192" s="23"/>
+      <c r="F192" s="23"/>
+      <c r="G192" s="23"/>
+      <c r="H192" s="23"/>
+      <c r="I192" s="23"/>
+      <c r="J192" s="23"/>
+      <c r="K192" s="24"/>
     </row>
     <row r="193" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B193" s="30" t="s">
+      <c r="B193" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C193" s="31"/>
-      <c r="D193" s="31" t="s">
+      <c r="C193" s="21"/>
+      <c r="D193" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="31"/>
-      <c r="F193" s="31" t="s">
+      <c r="E193" s="21"/>
+      <c r="F193" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G193" s="31"/>
-      <c r="H193" s="31"/>
-      <c r="I193" s="31"/>
-      <c r="J193" s="31" t="s">
+      <c r="G193" s="21"/>
+      <c r="H193" s="21"/>
+      <c r="I193" s="21"/>
+      <c r="J193" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K193" s="32"/>
+      <c r="K193" s="22"/>
     </row>
     <row r="194" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B194" s="26" t="s">
+      <c r="B194" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C194" s="23"/>
-      <c r="D194" s="23" t="s">
+      <c r="C194" s="17"/>
+      <c r="D194" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E194" s="23"/>
-      <c r="F194" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="G194" s="23"/>
-      <c r="H194" s="23"/>
-      <c r="I194" s="23"/>
-      <c r="J194" s="23" t="s">
+      <c r="E194" s="17"/>
+      <c r="F194" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G194" s="17"/>
+      <c r="H194" s="17"/>
+      <c r="I194" s="17"/>
+      <c r="J194" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K194" s="24"/>
+      <c r="K194" s="19"/>
     </row>
     <row r="195" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B195" s="16" t="s">
+      <c r="B195" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C195" s="81"/>
+      <c r="D195" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="C195" s="17"/>
-      <c r="D195" s="18" t="s">
+      <c r="E195" s="81"/>
+      <c r="F195" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="E195" s="17"/>
-      <c r="F195" s="19" t="s">
+      <c r="G195" s="84"/>
+      <c r="H195" s="84"/>
+      <c r="I195" s="85"/>
+      <c r="J195" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="G195" s="20"/>
-      <c r="H195" s="20"/>
-      <c r="I195" s="21"/>
-      <c r="J195" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K195" s="22"/>
+      <c r="K195" s="86"/>
     </row>
     <row r="196" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B196" s="26" t="s">
+      <c r="B196" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C196" s="23"/>
-      <c r="D196" s="23" t="s">
+      <c r="C196" s="17"/>
+      <c r="D196" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E196" s="23"/>
-      <c r="F196" s="25" t="s">
+      <c r="E196" s="17"/>
+      <c r="F196" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G196" s="23"/>
-      <c r="H196" s="23"/>
-      <c r="I196" s="23"/>
-      <c r="J196" s="23" t="s">
+      <c r="G196" s="17"/>
+      <c r="H196" s="17"/>
+      <c r="I196" s="17"/>
+      <c r="J196" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K196" s="24"/>
+      <c r="K196" s="19"/>
     </row>
     <row r="197" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B197" s="26" t="s">
+      <c r="B197" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C197" s="23"/>
-      <c r="D197" s="23" t="s">
+      <c r="C197" s="17"/>
+      <c r="D197" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E197" s="23"/>
-      <c r="F197" s="25" t="s">
+      <c r="E197" s="17"/>
+      <c r="F197" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G197" s="25"/>
-      <c r="H197" s="25"/>
-      <c r="I197" s="25"/>
-      <c r="J197" s="23" t="s">
+      <c r="G197" s="18"/>
+      <c r="H197" s="18"/>
+      <c r="I197" s="18"/>
+      <c r="J197" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K197" s="24"/>
+      <c r="K197" s="19"/>
     </row>
     <row r="198" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B198" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C198" s="23"/>
+      <c r="D198" s="23"/>
+      <c r="E198" s="23"/>
+      <c r="F198" s="23"/>
+      <c r="G198" s="23"/>
+      <c r="H198" s="23"/>
+      <c r="I198" s="23"/>
+      <c r="J198" s="23"/>
+      <c r="K198" s="24"/>
+    </row>
+    <row r="199" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B199" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C198" s="33"/>
-      <c r="D198" s="33"/>
-      <c r="E198" s="33"/>
-      <c r="F198" s="33"/>
-      <c r="G198" s="33"/>
-      <c r="H198" s="33"/>
-      <c r="I198" s="33"/>
-      <c r="J198" s="33"/>
-      <c r="K198" s="34"/>
-    </row>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B199" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C199" s="36"/>
-      <c r="D199" s="36"/>
-      <c r="E199" s="36"/>
-      <c r="F199" s="36"/>
-      <c r="G199" s="36"/>
-      <c r="H199" s="36"/>
-      <c r="I199" s="36"/>
-      <c r="J199" s="36"/>
-      <c r="K199" s="37"/>
+      <c r="C199" s="26"/>
+      <c r="D199" s="26"/>
+      <c r="E199" s="26"/>
+      <c r="F199" s="26"/>
+      <c r="G199" s="26"/>
+      <c r="H199" s="26"/>
+      <c r="I199" s="26"/>
+      <c r="J199" s="26"/>
+      <c r="K199" s="27"/>
     </row>
     <row r="200" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B200" s="38"/>
-      <c r="C200" s="36"/>
-      <c r="D200" s="36"/>
-      <c r="E200" s="36"/>
-      <c r="F200" s="36"/>
-      <c r="G200" s="36"/>
-      <c r="H200" s="36"/>
-      <c r="I200" s="36"/>
-      <c r="J200" s="36"/>
-      <c r="K200" s="37"/>
+      <c r="B200" s="28"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="26"/>
+      <c r="J200" s="26"/>
+      <c r="K200" s="27"/>
     </row>
     <row r="201" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B201" s="38"/>
-      <c r="C201" s="36"/>
-      <c r="D201" s="36"/>
-      <c r="E201" s="36"/>
-      <c r="F201" s="36"/>
-      <c r="G201" s="36"/>
-      <c r="H201" s="36"/>
-      <c r="I201" s="36"/>
-      <c r="J201" s="36"/>
-      <c r="K201" s="37"/>
+      <c r="B201" s="28"/>
+      <c r="C201" s="26"/>
+      <c r="D201" s="26"/>
+      <c r="E201" s="26"/>
+      <c r="F201" s="26"/>
+      <c r="G201" s="26"/>
+      <c r="H201" s="26"/>
+      <c r="I201" s="26"/>
+      <c r="J201" s="26"/>
+      <c r="K201" s="27"/>
     </row>
     <row r="202" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B202" s="39"/>
-      <c r="C202" s="40"/>
-      <c r="D202" s="40"/>
-      <c r="E202" s="40"/>
-      <c r="F202" s="40"/>
-      <c r="G202" s="40"/>
-      <c r="H202" s="40"/>
-      <c r="I202" s="40"/>
-      <c r="J202" s="40"/>
-      <c r="K202" s="41"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="30"/>
+      <c r="D202" s="30"/>
+      <c r="E202" s="30"/>
+      <c r="F202" s="30"/>
+      <c r="G202" s="30"/>
+      <c r="H202" s="30"/>
+      <c r="I202" s="30"/>
+      <c r="J202" s="30"/>
+      <c r="K202" s="31"/>
     </row>
     <row r="203" spans="2:11" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B203" s="42" t="s">
+      <c r="B203" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C203" s="43"/>
-      <c r="D203" s="43"/>
-      <c r="E203" s="43"/>
-      <c r="F203" s="43"/>
-      <c r="G203" s="43"/>
-      <c r="H203" s="43"/>
-      <c r="I203" s="43"/>
-      <c r="J203" s="43"/>
-      <c r="K203" s="44"/>
+      <c r="C203" s="33"/>
+      <c r="D203" s="33"/>
+      <c r="E203" s="33"/>
+      <c r="F203" s="33"/>
+      <c r="G203" s="33"/>
+      <c r="H203" s="33"/>
+      <c r="I203" s="33"/>
+      <c r="J203" s="33"/>
+      <c r="K203" s="34"/>
     </row>
     <row r="204" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B204" s="45" t="s">
+      <c r="B204" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C204" s="46"/>
-      <c r="D204" s="46"/>
-      <c r="E204" s="46"/>
-      <c r="F204" s="46"/>
-      <c r="G204" s="46"/>
-      <c r="H204" s="46"/>
-      <c r="I204" s="46"/>
-      <c r="J204" s="46"/>
-      <c r="K204" s="47"/>
+      <c r="C204" s="36"/>
+      <c r="D204" s="36"/>
+      <c r="E204" s="36"/>
+      <c r="F204" s="36"/>
+      <c r="G204" s="36"/>
+      <c r="H204" s="36"/>
+      <c r="I204" s="36"/>
+      <c r="J204" s="36"/>
+      <c r="K204" s="37"/>
     </row>
     <row r="205" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B205" s="30" t="s">
+      <c r="B205" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C205" s="31"/>
-      <c r="D205" s="31" t="s">
+      <c r="C205" s="21"/>
+      <c r="D205" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E205" s="31"/>
-      <c r="F205" s="31"/>
-      <c r="G205" s="31"/>
-      <c r="H205" s="31"/>
-      <c r="I205" s="31"/>
-      <c r="J205" s="31" t="s">
+      <c r="E205" s="21"/>
+      <c r="F205" s="21"/>
+      <c r="G205" s="21"/>
+      <c r="H205" s="21"/>
+      <c r="I205" s="21"/>
+      <c r="J205" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K205" s="32"/>
+      <c r="K205" s="22"/>
     </row>
     <row r="206" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B206" s="27" t="s">
+      <c r="B206" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C206" s="28"/>
-      <c r="D206" s="28" t="s">
+      <c r="C206" s="39"/>
+      <c r="D206" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E206" s="28"/>
-      <c r="F206" s="28"/>
-      <c r="G206" s="28"/>
-      <c r="H206" s="28"/>
-      <c r="I206" s="28"/>
-      <c r="J206" s="28" t="s">
+      <c r="E206" s="39"/>
+      <c r="F206" s="39"/>
+      <c r="G206" s="39"/>
+      <c r="H206" s="39"/>
+      <c r="I206" s="39"/>
+      <c r="J206" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="K206" s="29"/>
+      <c r="K206" s="40"/>
     </row>
     <row r="207" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B207" s="10" t="s">
@@ -4855,24 +4851,24 @@
       <c r="K207" s="12"/>
     </row>
     <row r="208" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B208" s="30" t="s">
+      <c r="B208" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C208" s="31"/>
-      <c r="D208" s="31" t="s">
+      <c r="C208" s="21"/>
+      <c r="D208" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="31"/>
-      <c r="F208" s="31" t="s">
+      <c r="E208" s="21"/>
+      <c r="F208" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G208" s="31"/>
-      <c r="H208" s="31"/>
-      <c r="I208" s="31"/>
-      <c r="J208" s="31" t="s">
+      <c r="G208" s="21"/>
+      <c r="H208" s="21"/>
+      <c r="I208" s="21"/>
+      <c r="J208" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K208" s="32"/>
+      <c r="K208" s="22"/>
     </row>
     <row r="209" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B209" s="5" t="s">
@@ -4944,11 +4940,303 @@
     </row>
     <row r="213" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="316">
+    <mergeCell ref="B210:C210"/>
+    <mergeCell ref="D210:E210"/>
+    <mergeCell ref="F210:I210"/>
+    <mergeCell ref="J210:K210"/>
+    <mergeCell ref="B211:K211"/>
+    <mergeCell ref="B212:K212"/>
+    <mergeCell ref="B195:C195"/>
+    <mergeCell ref="D195:E195"/>
+    <mergeCell ref="F195:I195"/>
+    <mergeCell ref="J195:K195"/>
+    <mergeCell ref="J196:K196"/>
+    <mergeCell ref="F196:I196"/>
+    <mergeCell ref="D196:E196"/>
+    <mergeCell ref="B196:C196"/>
+    <mergeCell ref="B206:C206"/>
+    <mergeCell ref="D206:I206"/>
+    <mergeCell ref="J206:K206"/>
+    <mergeCell ref="B207:K207"/>
+    <mergeCell ref="B208:C208"/>
+    <mergeCell ref="D208:E208"/>
+    <mergeCell ref="F208:I208"/>
+    <mergeCell ref="J208:K208"/>
+    <mergeCell ref="B209:C209"/>
+    <mergeCell ref="D209:E209"/>
+    <mergeCell ref="F209:I209"/>
+    <mergeCell ref="J209:K209"/>
+    <mergeCell ref="B197:C197"/>
+    <mergeCell ref="D197:E197"/>
+    <mergeCell ref="F197:I197"/>
+    <mergeCell ref="J197:K197"/>
+    <mergeCell ref="B198:K198"/>
+    <mergeCell ref="B199:K202"/>
+    <mergeCell ref="B203:K203"/>
+    <mergeCell ref="B204:K204"/>
+    <mergeCell ref="B205:C205"/>
+    <mergeCell ref="D205:I205"/>
+    <mergeCell ref="J205:K205"/>
+    <mergeCell ref="B191:C191"/>
+    <mergeCell ref="D191:I191"/>
+    <mergeCell ref="J191:K191"/>
+    <mergeCell ref="B192:K192"/>
+    <mergeCell ref="B193:C193"/>
+    <mergeCell ref="D193:E193"/>
+    <mergeCell ref="F193:I193"/>
+    <mergeCell ref="J193:K193"/>
+    <mergeCell ref="B194:C194"/>
+    <mergeCell ref="D194:E194"/>
+    <mergeCell ref="F194:I194"/>
+    <mergeCell ref="J194:K194"/>
+    <mergeCell ref="B182:K182"/>
+    <mergeCell ref="B183:K183"/>
+    <mergeCell ref="B184:K187"/>
+    <mergeCell ref="B188:C188"/>
+    <mergeCell ref="D188:F188"/>
+    <mergeCell ref="G188:H188"/>
+    <mergeCell ref="I188:K188"/>
+    <mergeCell ref="B189:K189"/>
+    <mergeCell ref="B190:K190"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="D148:E148"/>
+    <mergeCell ref="F148:I148"/>
+    <mergeCell ref="J148:K148"/>
+    <mergeCell ref="B149:K149"/>
+    <mergeCell ref="B150:K150"/>
+    <mergeCell ref="B145:K145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="D146:E146"/>
+    <mergeCell ref="F146:I146"/>
+    <mergeCell ref="J146:K146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="D147:E147"/>
+    <mergeCell ref="F147:I147"/>
+    <mergeCell ref="J147:K147"/>
+    <mergeCell ref="B136:K136"/>
+    <mergeCell ref="B137:K140"/>
+    <mergeCell ref="B141:K141"/>
+    <mergeCell ref="B142:K142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="D143:I143"/>
+    <mergeCell ref="J143:K143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="D144:I144"/>
+    <mergeCell ref="J144:K144"/>
+    <mergeCell ref="B133:K133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="D134:E134"/>
+    <mergeCell ref="F134:I134"/>
+    <mergeCell ref="J134:K134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="D135:E135"/>
+    <mergeCell ref="F135:I135"/>
+    <mergeCell ref="J135:K135"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="I129:K129"/>
+    <mergeCell ref="B130:K130"/>
+    <mergeCell ref="B131:K131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="D132:I132"/>
+    <mergeCell ref="J132:K132"/>
+    <mergeCell ref="B120:K120"/>
+    <mergeCell ref="B121:K121"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="F106:I106"/>
+    <mergeCell ref="J106:K106"/>
+    <mergeCell ref="B123:K123"/>
+    <mergeCell ref="B124:K124"/>
+    <mergeCell ref="B125:K128"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="D119:E119"/>
+    <mergeCell ref="F119:I119"/>
+    <mergeCell ref="J119:K119"/>
+    <mergeCell ref="B116:K116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="D117:E117"/>
+    <mergeCell ref="F117:I117"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="D118:E118"/>
+    <mergeCell ref="F118:I118"/>
+    <mergeCell ref="J118:K118"/>
+    <mergeCell ref="B107:K107"/>
+    <mergeCell ref="B108:K111"/>
+    <mergeCell ref="B112:K112"/>
+    <mergeCell ref="B113:K113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="D114:I114"/>
+    <mergeCell ref="J114:K114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="D115:I115"/>
+    <mergeCell ref="J115:K115"/>
+    <mergeCell ref="B101:K101"/>
+    <mergeCell ref="B102:K102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="D103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="B104:K104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="F105:I105"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B4:K28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:K29"/>
+    <mergeCell ref="B94:K94"/>
+    <mergeCell ref="B95:K95"/>
+    <mergeCell ref="B96:K99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="B33:K36"/>
+    <mergeCell ref="B52:K52"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="B46:K46"/>
+    <mergeCell ref="B47:K50"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="B42:K42"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="B38:K38"/>
+    <mergeCell ref="B39:K39"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="B55:K55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="B65:K65"/>
+    <mergeCell ref="B66:K69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B62:K62"/>
+    <mergeCell ref="B61:K61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="B31:K31"/>
+    <mergeCell ref="B32:K32"/>
+    <mergeCell ref="B74:K74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="F75:I75"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="B71:K71"/>
+    <mergeCell ref="B72:K72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="B51:K51"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:I53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="B64:K64"/>
+    <mergeCell ref="B76:K76"/>
+    <mergeCell ref="B77:K80"/>
+    <mergeCell ref="B81:K81"/>
+    <mergeCell ref="B82:K82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="D83:I83"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:I87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="F88:I88"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="B85:K85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F86:I86"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="B91:K91"/>
+    <mergeCell ref="B92:K92"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="F89:I89"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="F90:I90"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="B152:K152"/>
+    <mergeCell ref="B153:K153"/>
+    <mergeCell ref="B154:K157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="G158:H158"/>
+    <mergeCell ref="I158:K158"/>
+    <mergeCell ref="B159:K159"/>
+    <mergeCell ref="B160:K160"/>
+    <mergeCell ref="D173:I173"/>
+    <mergeCell ref="J173:K173"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="D174:I174"/>
+    <mergeCell ref="J174:K174"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="D161:I161"/>
+    <mergeCell ref="J161:K161"/>
+    <mergeCell ref="B162:K162"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="D163:E163"/>
+    <mergeCell ref="F163:I163"/>
+    <mergeCell ref="J163:K163"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="D164:E164"/>
+    <mergeCell ref="F164:I164"/>
+    <mergeCell ref="J164:K164"/>
     <mergeCell ref="B178:C178"/>
     <mergeCell ref="D178:E178"/>
     <mergeCell ref="F178:I178"/>
@@ -4973,298 +5261,6 @@
     <mergeCell ref="B171:K171"/>
     <mergeCell ref="B172:K172"/>
     <mergeCell ref="B173:C173"/>
-    <mergeCell ref="D173:I173"/>
-    <mergeCell ref="J173:K173"/>
-    <mergeCell ref="B174:C174"/>
-    <mergeCell ref="D174:I174"/>
-    <mergeCell ref="J174:K174"/>
-    <mergeCell ref="B161:C161"/>
-    <mergeCell ref="D161:I161"/>
-    <mergeCell ref="J161:K161"/>
-    <mergeCell ref="B162:K162"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="D163:E163"/>
-    <mergeCell ref="F163:I163"/>
-    <mergeCell ref="J163:K163"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="D164:E164"/>
-    <mergeCell ref="F164:I164"/>
-    <mergeCell ref="J164:K164"/>
-    <mergeCell ref="B152:K152"/>
-    <mergeCell ref="B153:K153"/>
-    <mergeCell ref="B154:K157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="G158:H158"/>
-    <mergeCell ref="I158:K158"/>
-    <mergeCell ref="B159:K159"/>
-    <mergeCell ref="B160:K160"/>
-    <mergeCell ref="B91:K91"/>
-    <mergeCell ref="B92:K92"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="F89:I89"/>
-    <mergeCell ref="J89:K89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="F90:I90"/>
-    <mergeCell ref="J90:K90"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="F88:I88"/>
-    <mergeCell ref="J88:K88"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="J84:K84"/>
-    <mergeCell ref="B85:K85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F86:I86"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="B76:K76"/>
-    <mergeCell ref="B77:K80"/>
-    <mergeCell ref="B81:K81"/>
-    <mergeCell ref="B82:K82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="D83:I83"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:I87"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="B31:K31"/>
-    <mergeCell ref="B32:K32"/>
-    <mergeCell ref="B74:K74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="B71:K71"/>
-    <mergeCell ref="B72:K72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="B51:K51"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:I53"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="B64:K64"/>
-    <mergeCell ref="B65:K65"/>
-    <mergeCell ref="B66:K69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B62:K62"/>
-    <mergeCell ref="B61:K61"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="B55:K55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D41:I41"/>
-    <mergeCell ref="B42:K42"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="B38:K38"/>
-    <mergeCell ref="B39:K39"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B4:K28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:K29"/>
-    <mergeCell ref="B94:K94"/>
-    <mergeCell ref="B95:K95"/>
-    <mergeCell ref="B96:K99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="B33:K36"/>
-    <mergeCell ref="B52:K52"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="B46:K46"/>
-    <mergeCell ref="B47:K50"/>
-    <mergeCell ref="B112:K112"/>
-    <mergeCell ref="B113:K113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="D114:I114"/>
-    <mergeCell ref="J114:K114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="D115:I115"/>
-    <mergeCell ref="J115:K115"/>
-    <mergeCell ref="B101:K101"/>
-    <mergeCell ref="B102:K102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="D103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="B104:K104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="F105:I105"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="B120:K120"/>
-    <mergeCell ref="B121:K121"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="F106:I106"/>
-    <mergeCell ref="J106:K106"/>
-    <mergeCell ref="B123:K123"/>
-    <mergeCell ref="B124:K124"/>
-    <mergeCell ref="B125:K128"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="D119:E119"/>
-    <mergeCell ref="F119:I119"/>
-    <mergeCell ref="J119:K119"/>
-    <mergeCell ref="B116:K116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="D117:E117"/>
-    <mergeCell ref="F117:I117"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="D118:E118"/>
-    <mergeCell ref="F118:I118"/>
-    <mergeCell ref="J118:K118"/>
-    <mergeCell ref="B107:K107"/>
-    <mergeCell ref="B108:K111"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="G129:H129"/>
-    <mergeCell ref="I129:K129"/>
-    <mergeCell ref="B130:K130"/>
-    <mergeCell ref="B131:K131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="D132:I132"/>
-    <mergeCell ref="J132:K132"/>
-    <mergeCell ref="B133:K133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="D134:E134"/>
-    <mergeCell ref="F134:I134"/>
-    <mergeCell ref="J134:K134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="D135:E135"/>
-    <mergeCell ref="F135:I135"/>
-    <mergeCell ref="J135:K135"/>
-    <mergeCell ref="B136:K136"/>
-    <mergeCell ref="B137:K140"/>
-    <mergeCell ref="B141:K141"/>
-    <mergeCell ref="B142:K142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="D143:I143"/>
-    <mergeCell ref="J143:K143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="D144:I144"/>
-    <mergeCell ref="J144:K144"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="D148:E148"/>
-    <mergeCell ref="F148:I148"/>
-    <mergeCell ref="J148:K148"/>
-    <mergeCell ref="B149:K149"/>
-    <mergeCell ref="B150:K150"/>
-    <mergeCell ref="B145:K145"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="D146:E146"/>
-    <mergeCell ref="F146:I146"/>
-    <mergeCell ref="J146:K146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="D147:E147"/>
-    <mergeCell ref="F147:I147"/>
-    <mergeCell ref="J147:K147"/>
-    <mergeCell ref="B182:K182"/>
-    <mergeCell ref="B183:K183"/>
-    <mergeCell ref="B184:K187"/>
-    <mergeCell ref="B188:C188"/>
-    <mergeCell ref="D188:F188"/>
-    <mergeCell ref="G188:H188"/>
-    <mergeCell ref="I188:K188"/>
-    <mergeCell ref="B189:K189"/>
-    <mergeCell ref="B190:K190"/>
-    <mergeCell ref="B191:C191"/>
-    <mergeCell ref="D191:I191"/>
-    <mergeCell ref="J191:K191"/>
-    <mergeCell ref="B192:K192"/>
-    <mergeCell ref="B193:C193"/>
-    <mergeCell ref="D193:E193"/>
-    <mergeCell ref="F193:I193"/>
-    <mergeCell ref="J193:K193"/>
-    <mergeCell ref="B194:C194"/>
-    <mergeCell ref="D194:E194"/>
-    <mergeCell ref="F194:I194"/>
-    <mergeCell ref="J194:K194"/>
-    <mergeCell ref="F209:I209"/>
-    <mergeCell ref="J209:K209"/>
-    <mergeCell ref="B197:C197"/>
-    <mergeCell ref="D197:E197"/>
-    <mergeCell ref="F197:I197"/>
-    <mergeCell ref="J197:K197"/>
-    <mergeCell ref="B198:K198"/>
-    <mergeCell ref="B199:K202"/>
-    <mergeCell ref="B203:K203"/>
-    <mergeCell ref="B204:K204"/>
-    <mergeCell ref="B205:C205"/>
-    <mergeCell ref="D205:I205"/>
-    <mergeCell ref="J205:K205"/>
-    <mergeCell ref="B210:C210"/>
-    <mergeCell ref="D210:E210"/>
-    <mergeCell ref="F210:I210"/>
-    <mergeCell ref="J210:K210"/>
-    <mergeCell ref="B211:K211"/>
-    <mergeCell ref="B212:K212"/>
-    <mergeCell ref="B195:C195"/>
-    <mergeCell ref="D195:E195"/>
-    <mergeCell ref="F195:I195"/>
-    <mergeCell ref="J195:K195"/>
-    <mergeCell ref="J196:K196"/>
-    <mergeCell ref="F196:I196"/>
-    <mergeCell ref="D196:E196"/>
-    <mergeCell ref="B196:C196"/>
-    <mergeCell ref="B206:C206"/>
-    <mergeCell ref="D206:I206"/>
-    <mergeCell ref="J206:K206"/>
-    <mergeCell ref="B207:K207"/>
-    <mergeCell ref="B208:C208"/>
-    <mergeCell ref="D208:E208"/>
-    <mergeCell ref="F208:I208"/>
-    <mergeCell ref="J208:K208"/>
-    <mergeCell ref="B209:C209"/>
-    <mergeCell ref="D209:E209"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
